--- a/pronosticos/plantilla_Antonio.xlsx
+++ b/pronosticos/plantilla_Antonio.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="231">
   <si>
     <t>PORRA DEL MUNDIAL 2026  —  PLANTILLA FASE DE GRUPOS</t>
   </si>
@@ -689,16 +689,25 @@
     <t>MVP del Torneo</t>
   </si>
   <si>
+    <t>Vitinha</t>
+  </si>
+  <si>
     <t>Mejor jugador del torneo (FIFA)</t>
   </si>
   <si>
     <t>Goleador del Torneo</t>
   </si>
   <si>
+    <t>Mbappé</t>
+  </si>
+  <si>
     <t>Maximo anotador · Bota de Oro FIFA</t>
   </si>
   <si>
     <t>Portero del Torneo</t>
+  </si>
+  <si>
+    <t>Thibaut Courtois</t>
   </si>
   <si>
     <t>Mejor portero · Guante de Oro FIFA</t>
@@ -913,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -955,6 +964,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="8" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -982,7 +994,7 @@
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -2364,95 +2376,95 @@
         <v>30</v>
       </c>
       <c r="D7" s="16">
-        <v>2.0</v>
-      </c>
-      <c r="E7" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E7" s="17">
         <v>0.0</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="20">
         <v>1.0</v>
       </c>
-      <c r="J7" s="20" t="str">
+      <c r="J7" s="21" t="str">
         <f t="array" ref="J7">INDEX(T7:T10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
         <v>México 🇲🇽</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="20">
         <f t="array" ref="K7">INDEX(U7:U10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
         <v>3</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="20">
         <f t="array" ref="L7">INDEX(V7:V10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
         <v>2</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="20">
         <f t="array" ref="M7">INDEX(W7:W10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
         <v>1</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="20">
         <f t="array" ref="N7">INDEX(X7:X10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
         <v>0</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="20">
         <f t="array" ref="O7">INDEX(Y7:Y10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
-        <v>5</v>
-      </c>
-      <c r="P7" s="19">
+        <v>4</v>
+      </c>
+      <c r="P7" s="20">
         <f t="array" ref="P7">INDEX(Z7:Z10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
         <v>2</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="20">
         <f t="array" ref="Q7">INDEX(AA7:AA10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
-        <v>3</v>
-      </c>
-      <c r="R7" s="19">
+        <v>2</v>
+      </c>
+      <c r="R7" s="20">
         <f t="array" ref="R7">INDEX(AB7:AB10,MATCH(LARGE(AC7:AC10,1),AC7:AC10,0))</f>
         <v>7</v>
       </c>
-      <c r="T7" s="21" t="str">
+      <c r="T7" s="22" t="str">
         <f>B7</f>
         <v>México 🇲🇽</v>
       </c>
-      <c r="U7" s="21">
+      <c r="U7" s="22">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(E7)),1,0)+IF(AND(ISNUMBER(D9),ISNUMBER(E9)),1,0)+IF(AND(ISNUMBER(D11),ISNUMBER(E11)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V7" s="21">
+      <c r="V7" s="22">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(E7),D7&gt;E7),1,0)+IF(AND(ISNUMBER(D9),ISNUMBER(E9),D9&gt;E9),1,0)+IF(AND(ISNUMBER(D11),ISNUMBER(E11),D11&gt;E11),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W7" s="21">
+      <c r="W7" s="22">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(E7),D7=E7),1,0)+IF(AND(ISNUMBER(D9),ISNUMBER(E9),D9=E9),1,0)+IF(AND(ISNUMBER(D11),ISNUMBER(E11),D11=E11),1,0)</f>
         <v>1</v>
       </c>
-      <c r="X7" s="21">
+      <c r="X7" s="22">
         <f t="shared" ref="X7:X10" si="2">U7-V7-W7</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="21">
+      <c r="Y7" s="22">
         <f t="shared" ref="Y7:Z7" si="1">IF(ISNUMBER(D7),D7,0)+IF(ISNUMBER(D9),D9,0)+IF(ISNUMBER(D11),D11,0)</f>
-        <v>5</v>
-      </c>
-      <c r="Z7" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z7" s="22">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AA7" s="21">
+      <c r="AA7" s="22">
         <f t="shared" ref="AA7:AA10" si="3">Y7-Z7</f>
-        <v>3</v>
-      </c>
-      <c r="AB7" s="21">
+        <v>2</v>
+      </c>
+      <c r="AB7" s="22">
         <f t="shared" ref="AB7:AB10" si="4">V7*3+W7</f>
         <v>7</v>
       </c>
-      <c r="AC7" s="21">
+      <c r="AC7" s="22">
         <f>AB7*1000000+(AA7+100)*1000+Y7*10+4</f>
-        <v>7103054</v>
+        <v>7102044</v>
       </c>
     </row>
     <row r="8">
@@ -2462,96 +2474,96 @@
       <c r="C8" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="17">
         <v>1.0</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="17">
         <v>1.0</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="20">
         <v>2.0</v>
       </c>
-      <c r="J8" s="20" t="str">
+      <c r="J8" s="21" t="str">
         <f t="array" ref="J8">INDEX(T7:T10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
         <v>🇨🇿 Chequia</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="20">
         <f t="array" ref="K8">INDEX(U7:U10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
         <v>3</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="20">
         <f t="array" ref="L8">INDEX(V7:V10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
         <v>1</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="20">
         <f t="array" ref="M8">INDEX(W7:W10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
         <v>2</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="20">
         <f t="array" ref="N8">INDEX(X7:X10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="20">
         <f t="array" ref="O8">INDEX(Y7:Y10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
         <v>4</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="20">
         <f t="array" ref="P8">INDEX(Z7:Z10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
-        <v>2</v>
-      </c>
-      <c r="Q8" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="20">
         <f t="array" ref="Q8">INDEX(AA7:AA10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R8" s="19">
+        <v>1</v>
+      </c>
+      <c r="R8" s="20">
         <f t="array" ref="R8">INDEX(AB7:AB10,MATCH(LARGE(AC7:AC10,2),AC7:AC10,0))</f>
         <v>5</v>
       </c>
-      <c r="T8" s="21" t="str">
+      <c r="T8" s="22" t="str">
         <f>F7</f>
         <v>🇿🇦 Sudáfrica</v>
       </c>
-      <c r="U8" s="21">
+      <c r="U8" s="22">
         <f>IF(AND(ISNUMBER(D10),ISNUMBER(E10)),1,0)+IF(AND(ISNUMBER(D12),ISNUMBER(E12)),1,0)+IF(AND(ISNUMBER(D7),ISNUMBER(E7)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V8" s="21">
+      <c r="V8" s="22">
         <f>IF(AND(ISNUMBER(D10),ISNUMBER(E10),D10&gt;E10),1,0)+IF(AND(ISNUMBER(D12),ISNUMBER(E12),D12&gt;E12),1,0)+IF(AND(ISNUMBER(D7),ISNUMBER(E7),E7&gt;D7),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W8" s="21">
+      <c r="W8" s="22">
         <f>IF(AND(ISNUMBER(D10),ISNUMBER(E10),D10=E10),1,0)+IF(AND(ISNUMBER(D12),ISNUMBER(E12),D12=E12),1,0)+IF(AND(ISNUMBER(D7),ISNUMBER(E7),D7=E7),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X8" s="21">
+      <c r="X8" s="22">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="Y8" s="21">
+      <c r="Y8" s="22">
         <f>IF(ISNUMBER(D10),D10,0)+IF(ISNUMBER(D12),D12,0)+IF(ISNUMBER(E7),E7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="21">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="22">
         <f>IF(ISNUMBER(E10),E10,0)+IF(ISNUMBER(E12),E12,0)+IF(ISNUMBER(D7),D7,0)</f>
-        <v>6</v>
-      </c>
-      <c r="AA8" s="21">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="22">
         <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="AB8" s="21">
+        <v>-3</v>
+      </c>
+      <c r="AB8" s="22">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AC8" s="21">
+      <c r="AC8" s="22">
         <f>AB8*1000000+(AA8+100)*1000+Y8*10+3</f>
-        <v>94003</v>
+        <v>97023</v>
       </c>
     </row>
     <row r="9">
@@ -2561,96 +2573,96 @@
       <c r="C9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="17">
         <v>2.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="17">
         <v>1.0</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="23">
         <v>3.0</v>
       </c>
-      <c r="J9" s="23" t="str">
+      <c r="J9" s="24" t="str">
         <f t="array" ref="J9">INDEX(T7:T10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
         <v>Corea del Sur 🇰🇷</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="23">
         <f t="array" ref="K9">INDEX(U7:U10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
         <v>3</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="23">
         <f t="array" ref="L9">INDEX(V7:V10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
         <v>1</v>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="23">
         <f t="array" ref="M9">INDEX(W7:W10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
         <v>1</v>
       </c>
-      <c r="N9" s="22">
+      <c r="N9" s="23">
         <f t="array" ref="N9">INDEX(X7:X10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
         <v>1</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="23">
         <f t="array" ref="O9">INDEX(Y7:Y10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
         <v>4</v>
       </c>
-      <c r="P9" s="22">
+      <c r="P9" s="23">
         <f t="array" ref="P9">INDEX(Z7:Z10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
-        <v>3</v>
-      </c>
-      <c r="Q9" s="22">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="23">
         <f t="array" ref="Q9">INDEX(AA7:AA10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
-        <v>1</v>
-      </c>
-      <c r="R9" s="22">
+        <v>0</v>
+      </c>
+      <c r="R9" s="23">
         <f t="array" ref="R9">INDEX(AB7:AB10,MATCH(LARGE(AC7:AC10,3),AC7:AC10,0))</f>
         <v>4</v>
       </c>
-      <c r="T9" s="21" t="str">
+      <c r="T9" s="22" t="str">
         <f>B8</f>
         <v>Corea del Sur 🇰🇷</v>
       </c>
-      <c r="U9" s="21">
+      <c r="U9" s="22">
         <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8)),1,0)+IF(AND(ISNUMBER(D9),ISNUMBER(E9)),1,0)+IF(AND(ISNUMBER(D12),ISNUMBER(E12)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V9" s="21">
+      <c r="V9" s="22">
         <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8),D8&gt;E8),1,0)+IF(AND(ISNUMBER(D9),ISNUMBER(E9),E9&gt;D9),1,0)+IF(AND(ISNUMBER(D12),ISNUMBER(E12),E12&gt;D12),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W9" s="21">
+      <c r="W9" s="22">
         <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8),D8=E8),1,0)+IF(AND(ISNUMBER(D9),ISNUMBER(E9),D9=E9),1,0)+IF(AND(ISNUMBER(D12),ISNUMBER(E12),D12=E12),1,0)</f>
         <v>1</v>
       </c>
-      <c r="X9" s="21">
+      <c r="X9" s="22">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Y9" s="21">
+      <c r="Y9" s="22">
         <f>IF(ISNUMBER(D8),D8,0)+IF(ISNUMBER(E9),E9,0)+IF(ISNUMBER(E12),E12,0)</f>
         <v>4</v>
       </c>
-      <c r="Z9" s="21">
+      <c r="Z9" s="22">
         <f>IF(ISNUMBER(E8),E8,0)+IF(ISNUMBER(D9),D9,0)+IF(ISNUMBER(D12),D12,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA9" s="21">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="22">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AB9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="22">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AC9" s="21">
+      <c r="AC9" s="22">
         <f>AB9*1000000+(AA9+100)*1000+Y9*10+2</f>
-        <v>4101042</v>
+        <v>4100042</v>
       </c>
     </row>
     <row r="10">
@@ -2661,95 +2673,95 @@
         <v>40</v>
       </c>
       <c r="D10" s="16">
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="17">
         <v>2.0</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="23">
         <v>4.0</v>
       </c>
-      <c r="J10" s="23" t="str">
+      <c r="J10" s="24" t="str">
         <f t="array" ref="J10">INDEX(T7:T10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
         <v>🇿🇦 Sudáfrica</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="23">
         <f t="array" ref="K10">INDEX(U7:U10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
         <v>3</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="23">
         <f t="array" ref="L10">INDEX(V7:V10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
         <v>0</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="23">
         <f t="array" ref="M10">INDEX(W7:W10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="22">
+      <c r="N10" s="23">
         <f t="array" ref="N10">INDEX(X7:X10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
         <v>3</v>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="23">
         <f t="array" ref="O10">INDEX(Y7:Y10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="22">
+        <v>2</v>
+      </c>
+      <c r="P10" s="23">
         <f t="array" ref="P10">INDEX(Z7:Z10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
-        <v>6</v>
-      </c>
-      <c r="Q10" s="22">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="23">
         <f t="array" ref="Q10">INDEX(AA7:AA10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
-        <v>-6</v>
-      </c>
-      <c r="R10" s="22">
+        <v>-3</v>
+      </c>
+      <c r="R10" s="23">
         <f t="array" ref="R10">INDEX(AB7:AB10,MATCH(LARGE(AC7:AC10,4),AC7:AC10,0))</f>
         <v>0</v>
       </c>
-      <c r="T10" s="21" t="str">
+      <c r="T10" s="22" t="str">
         <f>F8</f>
         <v>🇨🇿 Chequia</v>
       </c>
-      <c r="U10" s="21">
+      <c r="U10" s="22">
         <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8)),1,0)+IF(AND(ISNUMBER(D10),ISNUMBER(E10)),1,0)+IF(AND(ISNUMBER(D11),ISNUMBER(E11)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V10" s="21">
+      <c r="V10" s="22">
         <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8),E8&gt;D8),1,0)+IF(AND(ISNUMBER(D10),ISNUMBER(E10),E10&gt;D10),1,0)+IF(AND(ISNUMBER(D11),ISNUMBER(E11),E11&gt;D11),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W10" s="21">
+      <c r="W10" s="22">
         <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8),D8=E8),1,0)+IF(AND(ISNUMBER(D10),ISNUMBER(E10),D10=E10),1,0)+IF(AND(ISNUMBER(D11),ISNUMBER(E11),D11=E11),1,0)</f>
         <v>2</v>
       </c>
-      <c r="X10" s="21">
+      <c r="X10" s="22">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y10" s="21">
+      <c r="Y10" s="22">
         <f>IF(ISNUMBER(E8),E8,0)+IF(ISNUMBER(E10),E10,0)+IF(ISNUMBER(E11),E11,0)</f>
         <v>4</v>
       </c>
-      <c r="Z10" s="21">
+      <c r="Z10" s="22">
         <f>IF(ISNUMBER(D8),D8,0)+IF(ISNUMBER(D10),D10,0)+IF(ISNUMBER(D11),D11,0)</f>
-        <v>2</v>
-      </c>
-      <c r="AA10" s="21">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="22">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AB10" s="21">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="22">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="AC10" s="21">
+      <c r="AC10" s="22">
         <f>AB10*1000000+(AA10+100)*1000+Y10*10+1</f>
-        <v>5102041</v>
+        <v>5101041</v>
       </c>
     </row>
     <row r="11">
@@ -2759,16 +2771,16 @@
       <c r="C11" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="17">
         <v>1.0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="17">
         <v>1.0</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="19" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2780,20 +2792,20 @@
         <v>43</v>
       </c>
       <c r="D12" s="16">
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="16">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="17">
         <v>2.0</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="19" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" ht="18.0" customHeight="1">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="25" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="4"/>
@@ -2839,94 +2851,94 @@
       <c r="C14" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="17">
         <v>1.0</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <v>2.0</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <v>1.0</v>
       </c>
-      <c r="J14" s="20" t="str">
+      <c r="J14" s="21" t="str">
         <f t="array" ref="J14">INDEX(T14:T17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>🇨🇭 Suiza</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f t="array" ref="K14">INDEX(U14:U17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>3</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f t="array" ref="L14">INDEX(V14:V17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>3</v>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="20">
         <f t="array" ref="M14">INDEX(W14:W17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>0</v>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="20">
         <f t="array" ref="N14">INDEX(X14:X17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>0</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="20">
         <f t="array" ref="O14">INDEX(Y14:Y17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>7</v>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="20">
         <f t="array" ref="P14">INDEX(Z14:Z17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>1</v>
       </c>
-      <c r="Q14" s="19">
+      <c r="Q14" s="20">
         <f t="array" ref="Q14">INDEX(AA14:AA17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>6</v>
       </c>
-      <c r="R14" s="19">
+      <c r="R14" s="20">
         <f t="array" ref="R14">INDEX(AB14:AB17,MATCH(LARGE(AC14:AC17,1),AC14:AC17,0))</f>
         <v>9</v>
       </c>
-      <c r="T14" s="21" t="str">
+      <c r="T14" s="22" t="str">
         <f>B14</f>
         <v>Canadá 🇨🇦</v>
       </c>
-      <c r="U14" s="21">
+      <c r="U14" s="22">
         <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14)),1,0)+IF(AND(ISNUMBER(D16),ISNUMBER(E16)),1,0)+IF(AND(ISNUMBER(D18),ISNUMBER(E18)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V14" s="21">
+      <c r="V14" s="22">
         <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14),D14&gt;E14),1,0)+IF(AND(ISNUMBER(D16),ISNUMBER(E16),D16&gt;E16),1,0)+IF(AND(ISNUMBER(D18),ISNUMBER(E18),D18&gt;E18),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W14" s="21">
+      <c r="W14" s="22">
         <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14),D14=E14),1,0)+IF(AND(ISNUMBER(D16),ISNUMBER(E16),D16=E16),1,0)+IF(AND(ISNUMBER(D18),ISNUMBER(E18),D18=E18),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X14" s="21">
+      <c r="X14" s="22">
         <f t="shared" ref="X14:X17" si="6">U14-V14-W14</f>
         <v>1</v>
       </c>
-      <c r="Y14" s="21">
+      <c r="Y14" s="22">
         <f t="shared" ref="Y14:Z14" si="5">IF(ISNUMBER(D14),D14,0)+IF(ISNUMBER(D16),D16,0)+IF(ISNUMBER(D18),D18,0)</f>
         <v>5</v>
       </c>
-      <c r="Z14" s="21">
+      <c r="Z14" s="22">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="AA14" s="21">
+      <c r="AA14" s="22">
         <f t="shared" ref="AA14:AA17" si="7">Y14-Z14</f>
         <v>2</v>
       </c>
-      <c r="AB14" s="21">
+      <c r="AB14" s="22">
         <f t="shared" ref="AB14:AB17" si="8">V14*3+W14</f>
         <v>6</v>
       </c>
-      <c r="AC14" s="21">
+      <c r="AC14" s="22">
         <f>AB14*1000000+(AA14+100)*1000+Y14*10+4</f>
         <v>6102054</v>
       </c>
@@ -2939,93 +2951,93 @@
         <v>50</v>
       </c>
       <c r="D15" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="17">
         <v>1.0</v>
       </c>
-      <c r="E15" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <v>2.0</v>
       </c>
-      <c r="J15" s="20" t="str">
+      <c r="J15" s="21" t="str">
         <f t="array" ref="J15">INDEX(T14:T17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>Canadá 🇨🇦</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="20">
         <f t="array" ref="K15">INDEX(U14:U17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>3</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f t="array" ref="L15">INDEX(V14:V17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>2</v>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="20">
         <f t="array" ref="M15">INDEX(W14:W17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>0</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="20">
         <f t="array" ref="N15">INDEX(X14:X17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>1</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="20">
         <f t="array" ref="O15">INDEX(Y14:Y17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>5</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="20">
         <f t="array" ref="P15">INDEX(Z14:Z17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>3</v>
       </c>
-      <c r="Q15" s="19">
+      <c r="Q15" s="20">
         <f t="array" ref="Q15">INDEX(AA14:AA17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>2</v>
       </c>
-      <c r="R15" s="19">
+      <c r="R15" s="20">
         <f t="array" ref="R15">INDEX(AB14:AB17,MATCH(LARGE(AC14:AC17,2),AC14:AC17,0))</f>
         <v>6</v>
       </c>
-      <c r="T15" s="21" t="str">
+      <c r="T15" s="22" t="str">
         <f>F14</f>
         <v>🇨🇭 Suiza</v>
       </c>
-      <c r="U15" s="21">
+      <c r="U15" s="22">
         <f>IF(AND(ISNUMBER(D17),ISNUMBER(E17)),1,0)+IF(AND(ISNUMBER(D19),ISNUMBER(E19)),1,0)+IF(AND(ISNUMBER(D14),ISNUMBER(E14)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V15" s="21">
+      <c r="V15" s="22">
         <f>IF(AND(ISNUMBER(D17),ISNUMBER(E17),D17&gt;E17),1,0)+IF(AND(ISNUMBER(D19),ISNUMBER(E19),D19&gt;E19),1,0)+IF(AND(ISNUMBER(D14),ISNUMBER(E14),E14&gt;D14),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W15" s="21">
+      <c r="W15" s="22">
         <f>IF(AND(ISNUMBER(D17),ISNUMBER(E17),D17=E17),1,0)+IF(AND(ISNUMBER(D19),ISNUMBER(E19),D19=E19),1,0)+IF(AND(ISNUMBER(D14),ISNUMBER(E14),D14=E14),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X15" s="21">
+      <c r="X15" s="22">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Y15" s="21">
+      <c r="Y15" s="22">
         <f>IF(ISNUMBER(D17),D17,0)+IF(ISNUMBER(D19),D19,0)+IF(ISNUMBER(E14),E14,0)</f>
         <v>7</v>
       </c>
-      <c r="Z15" s="21">
+      <c r="Z15" s="22">
         <f>IF(ISNUMBER(E17),E17,0)+IF(ISNUMBER(E19),E19,0)+IF(ISNUMBER(D14),D14,0)</f>
         <v>1</v>
       </c>
-      <c r="AA15" s="21">
+      <c r="AA15" s="22">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="AB15" s="21">
+      <c r="AB15" s="22">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="AC15" s="21">
+      <c r="AC15" s="22">
         <f>AB15*1000000+(AA15+100)*1000+Y15*10+3</f>
         <v>9106073</v>
       </c>
@@ -3037,96 +3049,96 @@
       <c r="C16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <v>2.0</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="17">
         <v>0.0</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="23">
         <v>3.0</v>
       </c>
-      <c r="J16" s="23" t="str">
+      <c r="J16" s="24" t="str">
         <f t="array" ref="J16">INDEX(T14:T17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
         <v>🇧🇦 Bosnia y Herzegovina</v>
       </c>
-      <c r="K16" s="22">
+      <c r="K16" s="23">
         <f t="array" ref="K16">INDEX(U14:U17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
         <v>3</v>
       </c>
-      <c r="L16" s="22">
+      <c r="L16" s="23">
         <f t="array" ref="L16">INDEX(V14:V17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="22">
+        <v>1</v>
+      </c>
+      <c r="M16" s="23">
         <f t="array" ref="M16">INDEX(W14:W17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
-        <v>1</v>
-      </c>
-      <c r="N16" s="22">
+        <v>0</v>
+      </c>
+      <c r="N16" s="23">
         <f t="array" ref="N16">INDEX(X14:X17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
         <v>2</v>
       </c>
-      <c r="O16" s="22">
+      <c r="O16" s="23">
         <f t="array" ref="O16">INDEX(Y14:Y17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
         <v>2</v>
       </c>
-      <c r="P16" s="22">
+      <c r="P16" s="23">
         <f t="array" ref="P16">INDEX(Z14:Z17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
-        <v>5</v>
-      </c>
-      <c r="Q16" s="22">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="23">
         <f t="array" ref="Q16">INDEX(AA14:AA17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
-        <v>-3</v>
-      </c>
-      <c r="R16" s="22">
+        <v>-2</v>
+      </c>
+      <c r="R16" s="23">
         <f t="array" ref="R16">INDEX(AB14:AB17,MATCH(LARGE(AC14:AC17,3),AC14:AC17,0))</f>
-        <v>1</v>
-      </c>
-      <c r="T16" s="21" t="str">
+        <v>3</v>
+      </c>
+      <c r="T16" s="22" t="str">
         <f>B15</f>
         <v>Catar 🇶🇦</v>
       </c>
-      <c r="U16" s="21">
+      <c r="U16" s="22">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15)),1,0)+IF(AND(ISNUMBER(D16),ISNUMBER(E16)),1,0)+IF(AND(ISNUMBER(D19),ISNUMBER(E19)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V16" s="21">
+      <c r="V16" s="22">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15),D15&gt;E15),1,0)+IF(AND(ISNUMBER(D16),ISNUMBER(E16),E16&gt;D16),1,0)+IF(AND(ISNUMBER(D19),ISNUMBER(E19),E19&gt;D19),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W16" s="21">
+      <c r="W16" s="22">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15),D15=E15),1,0)+IF(AND(ISNUMBER(D16),ISNUMBER(E16),D16=E16),1,0)+IF(AND(ISNUMBER(D19),ISNUMBER(E19),D19=E19),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="X16" s="21">
+        <v>0</v>
+      </c>
+      <c r="X16" s="22">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="Y16" s="21">
+        <v>3</v>
+      </c>
+      <c r="Y16" s="22">
         <f>IF(ISNUMBER(D15),D15,0)+IF(ISNUMBER(E16),E16,0)+IF(ISNUMBER(E19),E19,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Z16" s="21">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="22">
         <f>IF(ISNUMBER(E15),E15,0)+IF(ISNUMBER(D16),D16,0)+IF(ISNUMBER(D19),D19,0)</f>
         <v>6</v>
       </c>
-      <c r="AA16" s="21">
+      <c r="AA16" s="22">
         <f t="shared" si="7"/>
-        <v>-5</v>
-      </c>
-      <c r="AB16" s="21">
+        <v>-6</v>
+      </c>
+      <c r="AB16" s="22">
         <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AC16" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="22">
         <f>AB16*1000000+(AA16+100)*1000+Y16*10+2</f>
-        <v>1095012</v>
+        <v>94002</v>
       </c>
     </row>
     <row r="17">
@@ -3136,96 +3148,96 @@
       <c r="C17" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <v>2.0</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="17">
         <v>0.0</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="23">
         <v>4.0</v>
       </c>
-      <c r="J17" s="23" t="str">
+      <c r="J17" s="24" t="str">
         <f t="array" ref="J17">INDEX(T14:T17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
         <v>Catar 🇶🇦</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="23">
         <f t="array" ref="K17">INDEX(U14:U17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
         <v>3</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="23">
         <f t="array" ref="L17">INDEX(V14:V17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
         <v>0</v>
       </c>
-      <c r="M17" s="22">
+      <c r="M17" s="23">
         <f t="array" ref="M17">INDEX(W14:W17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
-        <v>1</v>
-      </c>
-      <c r="N17" s="22">
+        <v>0</v>
+      </c>
+      <c r="N17" s="23">
         <f t="array" ref="N17">INDEX(X14:X17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
-        <v>2</v>
-      </c>
-      <c r="O17" s="22">
+        <v>3</v>
+      </c>
+      <c r="O17" s="23">
         <f t="array" ref="O17">INDEX(Y14:Y17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
-        <v>1</v>
-      </c>
-      <c r="P17" s="22">
+        <v>0</v>
+      </c>
+      <c r="P17" s="23">
         <f t="array" ref="P17">INDEX(Z14:Z17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
         <v>6</v>
       </c>
-      <c r="Q17" s="22">
+      <c r="Q17" s="23">
         <f t="array" ref="Q17">INDEX(AA14:AA17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
-        <v>-5</v>
-      </c>
-      <c r="R17" s="22">
+        <v>-6</v>
+      </c>
+      <c r="R17" s="23">
         <f t="array" ref="R17">INDEX(AB14:AB17,MATCH(LARGE(AC14:AC17,4),AC14:AC17,0))</f>
-        <v>1</v>
-      </c>
-      <c r="T17" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="T17" s="22" t="str">
         <f>F15</f>
         <v>🇧🇦 Bosnia y Herzegovina</v>
       </c>
-      <c r="U17" s="21">
+      <c r="U17" s="22">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15)),1,0)+IF(AND(ISNUMBER(D17),ISNUMBER(E17)),1,0)+IF(AND(ISNUMBER(D18),ISNUMBER(E18)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V17" s="21">
+      <c r="V17" s="22">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15),E15&gt;D15),1,0)+IF(AND(ISNUMBER(D17),ISNUMBER(E17),E17&gt;D17),1,0)+IF(AND(ISNUMBER(D18),ISNUMBER(E18),E18&gt;D18),1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="W17" s="21">
+        <v>1</v>
+      </c>
+      <c r="W17" s="22">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15),D15=E15),1,0)+IF(AND(ISNUMBER(D17),ISNUMBER(E17),D17=E17),1,0)+IF(AND(ISNUMBER(D18),ISNUMBER(E18),D18=E18),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="X17" s="21">
+        <v>0</v>
+      </c>
+      <c r="X17" s="22">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="Y17" s="21">
+      <c r="Y17" s="22">
         <f>IF(ISNUMBER(E15),E15,0)+IF(ISNUMBER(E17),E17,0)+IF(ISNUMBER(E18),E18,0)</f>
         <v>2</v>
       </c>
-      <c r="Z17" s="21">
+      <c r="Z17" s="22">
         <f>IF(ISNUMBER(D15),D15,0)+IF(ISNUMBER(D17),D17,0)+IF(ISNUMBER(D18),D18,0)</f>
-        <v>5</v>
-      </c>
-      <c r="AA17" s="21">
+        <v>4</v>
+      </c>
+      <c r="AA17" s="22">
         <f t="shared" si="7"/>
-        <v>-3</v>
-      </c>
-      <c r="AB17" s="21">
+        <v>-2</v>
+      </c>
+      <c r="AB17" s="22">
         <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AC17" s="21">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="22">
         <f>AB17*1000000+(AA17+100)*1000+Y17*10+1</f>
-        <v>1097021</v>
+        <v>3098021</v>
       </c>
     </row>
     <row r="18">
@@ -3235,16 +3247,16 @@
       <c r="C18" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="17">
         <v>2.0</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="17">
         <v>1.0</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="19" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3255,21 +3267,21 @@
       <c r="C19" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="17">
         <v>3.0</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="17">
         <v>0.0</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="19" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20" ht="18.0" customHeight="1">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="25" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="4"/>
@@ -3315,94 +3327,94 @@
       <c r="C21" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <v>2.0</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="17">
         <v>1.0</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <v>1.0</v>
       </c>
-      <c r="J21" s="20" t="str">
+      <c r="J21" s="21" t="str">
         <f t="array" ref="J21">INDEX(T21:T24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>Brasil 🇧🇷</v>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="20">
         <f t="array" ref="K21">INDEX(U21:U24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>3</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="20">
         <f t="array" ref="L21">INDEX(V21:V24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>3</v>
       </c>
-      <c r="M21" s="19">
+      <c r="M21" s="20">
         <f t="array" ref="M21">INDEX(W21:W24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="20">
         <f t="array" ref="N21">INDEX(X21:X24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="O21" s="19">
+      <c r="O21" s="20">
         <f t="array" ref="O21">INDEX(Y21:Y24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>9</v>
       </c>
-      <c r="P21" s="19">
+      <c r="P21" s="20">
         <f t="array" ref="P21">INDEX(Z21:Z24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>1</v>
       </c>
-      <c r="Q21" s="19">
+      <c r="Q21" s="20">
         <f t="array" ref="Q21">INDEX(AA21:AA24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>8</v>
       </c>
-      <c r="R21" s="19">
+      <c r="R21" s="20">
         <f t="array" ref="R21">INDEX(AB21:AB24,MATCH(LARGE(AC21:AC24,1),AC21:AC24,0))</f>
         <v>9</v>
       </c>
-      <c r="T21" s="21" t="str">
+      <c r="T21" s="22" t="str">
         <f>B21</f>
         <v>Brasil 🇧🇷</v>
       </c>
-      <c r="U21" s="21">
+      <c r="U21" s="22">
         <f>IF(AND(ISNUMBER(D21),ISNUMBER(E21)),1,0)+IF(AND(ISNUMBER(D23),ISNUMBER(E23)),1,0)+IF(AND(ISNUMBER(D25),ISNUMBER(E25)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V21" s="21">
+      <c r="V21" s="22">
         <f>IF(AND(ISNUMBER(D21),ISNUMBER(E21),D21&gt;E21),1,0)+IF(AND(ISNUMBER(D23),ISNUMBER(E23),D23&gt;E23),1,0)+IF(AND(ISNUMBER(D25),ISNUMBER(E25),D25&gt;E25),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W21" s="21">
+      <c r="W21" s="22">
         <f>IF(AND(ISNUMBER(D21),ISNUMBER(E21),D21=E21),1,0)+IF(AND(ISNUMBER(D23),ISNUMBER(E23),D23=E23),1,0)+IF(AND(ISNUMBER(D25),ISNUMBER(E25),D25=E25),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X21" s="21">
+      <c r="X21" s="22">
         <f t="shared" ref="X21:X24" si="10">U21-V21-W21</f>
         <v>0</v>
       </c>
-      <c r="Y21" s="21">
+      <c r="Y21" s="22">
         <f t="shared" ref="Y21:Z21" si="9">IF(ISNUMBER(D21),D21,0)+IF(ISNUMBER(D23),D23,0)+IF(ISNUMBER(D25),D25,0)</f>
         <v>9</v>
       </c>
-      <c r="Z21" s="21">
+      <c r="Z21" s="22">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AA21" s="21">
+      <c r="AA21" s="22">
         <f t="shared" ref="AA21:AA24" si="11">Y21-Z21</f>
         <v>8</v>
       </c>
-      <c r="AB21" s="21">
+      <c r="AB21" s="22">
         <f t="shared" ref="AB21:AB24" si="12">V21*3+W21</f>
         <v>9</v>
       </c>
-      <c r="AC21" s="21">
+      <c r="AC21" s="22">
         <f>AB21*1000000+(AA21+100)*1000+Y21*10+4</f>
         <v>9108094</v>
       </c>
@@ -3414,94 +3426,94 @@
       <c r="C22" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <v>2.0</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="17">
         <v>0.0</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <v>2.0</v>
       </c>
-      <c r="J22" s="20" t="str">
+      <c r="J22" s="21" t="str">
         <f t="array" ref="J22">INDEX(T21:T24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>🇲🇦 Marruecos</v>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="20">
         <f t="array" ref="K22">INDEX(U21:U24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>3</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="20">
         <f t="array" ref="L22">INDEX(V21:V24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>2</v>
       </c>
-      <c r="M22" s="19">
+      <c r="M22" s="20">
         <f t="array" ref="M22">INDEX(W21:W24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="20">
         <f t="array" ref="N22">INDEX(X21:X24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>1</v>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="20">
         <f t="array" ref="O22">INDEX(Y21:Y24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>6</v>
       </c>
-      <c r="P22" s="19">
+      <c r="P22" s="20">
         <f t="array" ref="P22">INDEX(Z21:Z24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>2</v>
       </c>
-      <c r="Q22" s="19">
+      <c r="Q22" s="20">
         <f t="array" ref="Q22">INDEX(AA21:AA24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>4</v>
       </c>
-      <c r="R22" s="19">
+      <c r="R22" s="20">
         <f t="array" ref="R22">INDEX(AB21:AB24,MATCH(LARGE(AC21:AC24,2),AC21:AC24,0))</f>
         <v>6</v>
       </c>
-      <c r="T22" s="21" t="str">
+      <c r="T22" s="22" t="str">
         <f>F21</f>
         <v>🇲🇦 Marruecos</v>
       </c>
-      <c r="U22" s="21">
+      <c r="U22" s="22">
         <f>IF(AND(ISNUMBER(D24),ISNUMBER(E24)),1,0)+IF(AND(ISNUMBER(D26),ISNUMBER(E26)),1,0)+IF(AND(ISNUMBER(D21),ISNUMBER(E21)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V22" s="21">
+      <c r="V22" s="22">
         <f>IF(AND(ISNUMBER(D24),ISNUMBER(E24),D24&gt;E24),1,0)+IF(AND(ISNUMBER(D26),ISNUMBER(E26),D26&gt;E26),1,0)+IF(AND(ISNUMBER(D21),ISNUMBER(E21),E21&gt;D21),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W22" s="21">
+      <c r="W22" s="22">
         <f>IF(AND(ISNUMBER(D24),ISNUMBER(E24),D24=E24),1,0)+IF(AND(ISNUMBER(D26),ISNUMBER(E26),D26=E26),1,0)+IF(AND(ISNUMBER(D21),ISNUMBER(E21),D21=E21),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X22" s="21">
+      <c r="X22" s="22">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Y22" s="21">
+      <c r="Y22" s="22">
         <f>IF(ISNUMBER(D24),D24,0)+IF(ISNUMBER(D26),D26,0)+IF(ISNUMBER(E21),E21,0)</f>
         <v>6</v>
       </c>
-      <c r="Z22" s="21">
+      <c r="Z22" s="22">
         <f>IF(ISNUMBER(E24),E24,0)+IF(ISNUMBER(E26),E26,0)+IF(ISNUMBER(D21),D21,0)</f>
         <v>2</v>
       </c>
-      <c r="AA22" s="21">
+      <c r="AA22" s="22">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="AB22" s="21">
+      <c r="AB22" s="22">
         <f t="shared" si="12"/>
         <v>6</v>
       </c>
-      <c r="AC22" s="21">
+      <c r="AC22" s="22">
         <f>AB22*1000000+(AA22+100)*1000+Y22*10+3</f>
         <v>6104063</v>
       </c>
@@ -3513,94 +3525,94 @@
       <c r="C23" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>3.0</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <v>0.0</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="23">
         <v>3.0</v>
       </c>
-      <c r="J23" s="23" t="str">
+      <c r="J23" s="24" t="str">
         <f t="array" ref="J23">INDEX(T21:T24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>Escocia 🏴󠁧󠁢󠁳󠁣󠁴󠁿</v>
       </c>
-      <c r="K23" s="22">
+      <c r="K23" s="23">
         <f t="array" ref="K23">INDEX(U21:U24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>3</v>
       </c>
-      <c r="L23" s="22">
+      <c r="L23" s="23">
         <f t="array" ref="L23">INDEX(V21:V24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>1</v>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="23">
         <f t="array" ref="M23">INDEX(W21:W24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="23">
         <f t="array" ref="N23">INDEX(X21:X24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>2</v>
       </c>
-      <c r="O23" s="22">
+      <c r="O23" s="23">
         <f t="array" ref="O23">INDEX(Y21:Y24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>2</v>
       </c>
-      <c r="P23" s="22">
+      <c r="P23" s="23">
         <f t="array" ref="P23">INDEX(Z21:Z24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>5</v>
       </c>
-      <c r="Q23" s="22">
+      <c r="Q23" s="23">
         <f t="array" ref="Q23">INDEX(AA21:AA24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>-3</v>
       </c>
-      <c r="R23" s="22">
+      <c r="R23" s="23">
         <f t="array" ref="R23">INDEX(AB21:AB24,MATCH(LARGE(AC21:AC24,3),AC21:AC24,0))</f>
         <v>3</v>
       </c>
-      <c r="T23" s="21" t="str">
+      <c r="T23" s="22" t="str">
         <f>B22</f>
         <v>Escocia 🏴󠁧󠁢󠁳󠁣󠁴󠁿</v>
       </c>
-      <c r="U23" s="21">
+      <c r="U23" s="22">
         <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22)),1,0)+IF(AND(ISNUMBER(D23),ISNUMBER(E23)),1,0)+IF(AND(ISNUMBER(D26),ISNUMBER(E26)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V23" s="21">
+      <c r="V23" s="22">
         <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22),D22&gt;E22),1,0)+IF(AND(ISNUMBER(D23),ISNUMBER(E23),E23&gt;D23),1,0)+IF(AND(ISNUMBER(D26),ISNUMBER(E26),E26&gt;D26),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W23" s="21">
+      <c r="W23" s="22">
         <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22),D22=E22),1,0)+IF(AND(ISNUMBER(D23),ISNUMBER(E23),D23=E23),1,0)+IF(AND(ISNUMBER(D26),ISNUMBER(E26),D26=E26),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X23" s="21">
+      <c r="X23" s="22">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="Y23" s="21">
+      <c r="Y23" s="22">
         <f>IF(ISNUMBER(D22),D22,0)+IF(ISNUMBER(E23),E23,0)+IF(ISNUMBER(E26),E26,0)</f>
         <v>2</v>
       </c>
-      <c r="Z23" s="21">
+      <c r="Z23" s="22">
         <f>IF(ISNUMBER(E22),E22,0)+IF(ISNUMBER(D23),D23,0)+IF(ISNUMBER(D26),D26,0)</f>
         <v>5</v>
       </c>
-      <c r="AA23" s="21">
+      <c r="AA23" s="22">
         <f t="shared" si="11"/>
         <v>-3</v>
       </c>
-      <c r="AB23" s="21">
+      <c r="AB23" s="22">
         <f t="shared" si="12"/>
         <v>3</v>
       </c>
-      <c r="AC23" s="21">
+      <c r="AC23" s="22">
         <f>AB23*1000000+(AA23+100)*1000+Y23*10+2</f>
         <v>3097022</v>
       </c>
@@ -3612,94 +3624,94 @@
       <c r="C24" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>3.0</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>0.0</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="23">
         <v>4.0</v>
       </c>
-      <c r="J24" s="23" t="str">
+      <c r="J24" s="24" t="str">
         <f t="array" ref="J24">INDEX(T21:T24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>🇭🇹 Haití</v>
       </c>
-      <c r="K24" s="22">
+      <c r="K24" s="23">
         <f t="array" ref="K24">INDEX(U21:U24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>3</v>
       </c>
-      <c r="L24" s="22">
+      <c r="L24" s="23">
         <f t="array" ref="L24">INDEX(V21:V24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="M24" s="22">
+      <c r="M24" s="23">
         <f t="array" ref="M24">INDEX(W21:W24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="N24" s="22">
+      <c r="N24" s="23">
         <f t="array" ref="N24">INDEX(X21:X24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>3</v>
       </c>
-      <c r="O24" s="22">
+      <c r="O24" s="23">
         <f t="array" ref="O24">INDEX(Y21:Y24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="P24" s="22">
+      <c r="P24" s="23">
         <f t="array" ref="P24">INDEX(Z21:Z24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>9</v>
       </c>
-      <c r="Q24" s="22">
+      <c r="Q24" s="23">
         <f t="array" ref="Q24">INDEX(AA21:AA24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>-9</v>
       </c>
-      <c r="R24" s="22">
+      <c r="R24" s="23">
         <f t="array" ref="R24">INDEX(AB21:AB24,MATCH(LARGE(AC21:AC24,4),AC21:AC24,0))</f>
         <v>0</v>
       </c>
-      <c r="T24" s="21" t="str">
+      <c r="T24" s="22" t="str">
         <f>F22</f>
         <v>🇭🇹 Haití</v>
       </c>
-      <c r="U24" s="21">
+      <c r="U24" s="22">
         <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22)),1,0)+IF(AND(ISNUMBER(D24),ISNUMBER(E24)),1,0)+IF(AND(ISNUMBER(D25),ISNUMBER(E25)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V24" s="21">
+      <c r="V24" s="22">
         <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22),E22&gt;D22),1,0)+IF(AND(ISNUMBER(D24),ISNUMBER(E24),E24&gt;D24),1,0)+IF(AND(ISNUMBER(D25),ISNUMBER(E25),E25&gt;D25),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W24" s="21">
+      <c r="W24" s="22">
         <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22),D22=E22),1,0)+IF(AND(ISNUMBER(D24),ISNUMBER(E24),D24=E24),1,0)+IF(AND(ISNUMBER(D25),ISNUMBER(E25),D25=E25),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X24" s="21">
+      <c r="X24" s="22">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="Y24" s="21">
+      <c r="Y24" s="22">
         <f>IF(ISNUMBER(E22),E22,0)+IF(ISNUMBER(E24),E24,0)+IF(ISNUMBER(E25),E25,0)</f>
         <v>0</v>
       </c>
-      <c r="Z24" s="21">
+      <c r="Z24" s="22">
         <f>IF(ISNUMBER(D22),D22,0)+IF(ISNUMBER(D24),D24,0)+IF(ISNUMBER(D25),D25,0)</f>
         <v>9</v>
       </c>
-      <c r="AA24" s="21">
+      <c r="AA24" s="22">
         <f t="shared" si="11"/>
         <v>-9</v>
       </c>
-      <c r="AB24" s="21">
+      <c r="AB24" s="22">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AC24" s="21">
+      <c r="AC24" s="22">
         <f>AB24*1000000+(AA24+100)*1000+Y24*10+1</f>
         <v>91001</v>
       </c>
@@ -3711,16 +3723,16 @@
       <c r="C25" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="17">
         <v>4.0</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="17">
         <v>0.0</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="19" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3731,21 +3743,21 @@
       <c r="C26" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <v>2.0</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="17">
         <v>0.0</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="19" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="27" ht="18.0" customHeight="1">
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="25" t="s">
         <v>76</v>
       </c>
       <c r="C27" s="4"/>
@@ -3791,94 +3803,94 @@
       <c r="C28" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="17">
         <v>2.0</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="17">
         <v>1.0</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <v>1.0</v>
       </c>
-      <c r="J28" s="20" t="str">
+      <c r="J28" s="21" t="str">
         <f t="array" ref="J28">INDEX(T28:T31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>Estados Unidos 🇺🇸</v>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="20">
         <f t="array" ref="K28">INDEX(U28:U31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>3</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="20">
         <f t="array" ref="L28">INDEX(V28:V31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>2</v>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="20">
         <f t="array" ref="M28">INDEX(W28:W31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>1</v>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="20">
         <f t="array" ref="N28">INDEX(X28:X31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>0</v>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="20">
         <f t="array" ref="O28">INDEX(Y28:Y31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>6</v>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="20">
         <f t="array" ref="P28">INDEX(Z28:Z31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>3</v>
       </c>
-      <c r="Q28" s="19">
+      <c r="Q28" s="20">
         <f t="array" ref="Q28">INDEX(AA28:AA31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>3</v>
       </c>
-      <c r="R28" s="19">
+      <c r="R28" s="20">
         <f t="array" ref="R28">INDEX(AB28:AB31,MATCH(LARGE(AC28:AC31,1),AC28:AC31,0))</f>
         <v>7</v>
       </c>
-      <c r="T28" s="21" t="str">
+      <c r="T28" s="22" t="str">
         <f>B28</f>
         <v>Estados Unidos 🇺🇸</v>
       </c>
-      <c r="U28" s="21">
+      <c r="U28" s="22">
         <f>IF(AND(ISNUMBER(D28),ISNUMBER(E28)),1,0)+IF(AND(ISNUMBER(D30),ISNUMBER(E30)),1,0)+IF(AND(ISNUMBER(D32),ISNUMBER(E32)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V28" s="21">
+      <c r="V28" s="22">
         <f>IF(AND(ISNUMBER(D28),ISNUMBER(E28),D28&gt;E28),1,0)+IF(AND(ISNUMBER(D30),ISNUMBER(E30),D30&gt;E30),1,0)+IF(AND(ISNUMBER(D32),ISNUMBER(E32),D32&gt;E32),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W28" s="21">
+      <c r="W28" s="22">
         <f>IF(AND(ISNUMBER(D28),ISNUMBER(E28),D28=E28),1,0)+IF(AND(ISNUMBER(D30),ISNUMBER(E30),D30=E30),1,0)+IF(AND(ISNUMBER(D32),ISNUMBER(E32),D32=E32),1,0)</f>
         <v>1</v>
       </c>
-      <c r="X28" s="21">
+      <c r="X28" s="22">
         <f t="shared" ref="X28:X31" si="14">U28-V28-W28</f>
         <v>0</v>
       </c>
-      <c r="Y28" s="21">
+      <c r="Y28" s="22">
         <f t="shared" ref="Y28:Z28" si="13">IF(ISNUMBER(D28),D28,0)+IF(ISNUMBER(D30),D30,0)+IF(ISNUMBER(D32),D32,0)</f>
         <v>6</v>
       </c>
-      <c r="Z28" s="21">
+      <c r="Z28" s="22">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
-      <c r="AA28" s="21">
+      <c r="AA28" s="22">
         <f t="shared" ref="AA28:AA31" si="15">Y28-Z28</f>
         <v>3</v>
       </c>
-      <c r="AB28" s="21">
+      <c r="AB28" s="22">
         <f t="shared" ref="AB28:AB31" si="16">V28*3+W28</f>
         <v>7</v>
       </c>
-      <c r="AC28" s="21">
+      <c r="AC28" s="22">
         <f>AB28*1000000+(AA28+100)*1000+Y28*10+4</f>
         <v>7103064</v>
       </c>
@@ -3890,96 +3902,96 @@
       <c r="C29" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="17">
         <v>1.0</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="17">
         <v>2.0</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <v>2.0</v>
       </c>
-      <c r="J29" s="20" t="str">
+      <c r="J29" s="21" t="str">
         <f t="array" ref="J29">INDEX(T28:T31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
         <v>🇹🇷 Turquía</v>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="20">
         <f t="array" ref="K29">INDEX(U28:U31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
         <v>3</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="20">
         <f t="array" ref="L29">INDEX(V28:V31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
+        <v>2</v>
+      </c>
+      <c r="M29" s="20">
+        <f t="array" ref="M29">INDEX(W28:W31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
         <v>1</v>
       </c>
-      <c r="M29" s="19">
-        <f t="array" ref="M29">INDEX(W28:W31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
-        <v>2</v>
-      </c>
-      <c r="N29" s="19">
+      <c r="N29" s="20">
         <f t="array" ref="N29">INDEX(X28:X31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
         <v>0</v>
       </c>
-      <c r="O29" s="19">
+      <c r="O29" s="20">
         <f t="array" ref="O29">INDEX(Y28:Y31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
-        <v>5</v>
-      </c>
-      <c r="P29" s="19">
+        <v>6</v>
+      </c>
+      <c r="P29" s="20">
         <f t="array" ref="P29">INDEX(Z28:Z31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
         <v>4</v>
       </c>
-      <c r="Q29" s="19">
+      <c r="Q29" s="20">
         <f t="array" ref="Q29">INDEX(AA28:AA31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
-        <v>1</v>
-      </c>
-      <c r="R29" s="19">
+        <v>2</v>
+      </c>
+      <c r="R29" s="20">
         <f t="array" ref="R29">INDEX(AB28:AB31,MATCH(LARGE(AC28:AC31,2),AC28:AC31,0))</f>
-        <v>5</v>
-      </c>
-      <c r="T29" s="21" t="str">
+        <v>7</v>
+      </c>
+      <c r="T29" s="22" t="str">
         <f>F28</f>
         <v>🇵🇾 Paraguay</v>
       </c>
-      <c r="U29" s="21">
+      <c r="U29" s="22">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(E31)),1,0)+IF(AND(ISNUMBER(D33),ISNUMBER(E33)),1,0)+IF(AND(ISNUMBER(D28),ISNUMBER(E28)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V29" s="21">
+      <c r="V29" s="22">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(E31),D31&gt;E31),1,0)+IF(AND(ISNUMBER(D33),ISNUMBER(E33),D33&gt;E33),1,0)+IF(AND(ISNUMBER(D28),ISNUMBER(E28),E28&gt;D28),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W29" s="21">
+      <c r="W29" s="22">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(E31),D31=E31),1,0)+IF(AND(ISNUMBER(D33),ISNUMBER(E33),D33=E33),1,0)+IF(AND(ISNUMBER(D28),ISNUMBER(E28),D28=E28),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="X29" s="21">
+        <v>0</v>
+      </c>
+      <c r="X29" s="22">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="Y29" s="21">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="22">
         <f>IF(ISNUMBER(D31),D31,0)+IF(ISNUMBER(D33),D33,0)+IF(ISNUMBER(E28),E28,0)</f>
-        <v>3</v>
-      </c>
-      <c r="Z29" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="22">
         <f>IF(ISNUMBER(E31),E31,0)+IF(ISNUMBER(E33),E33,0)+IF(ISNUMBER(D28),D28,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA29" s="21">
+        <v>4</v>
+      </c>
+      <c r="AA29" s="22">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="21">
+      <c r="AB29" s="22">
         <f t="shared" si="16"/>
-        <v>4</v>
-      </c>
-      <c r="AC29" s="21">
+        <v>3</v>
+      </c>
+      <c r="AC29" s="22">
         <f>AB29*1000000+(AA29+100)*1000+Y29*10+3</f>
-        <v>4100033</v>
+        <v>3100043</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -3989,96 +4001,96 @@
       <c r="C30" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="17">
         <v>2.0</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <v>0.0</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="23">
         <v>3.0</v>
       </c>
-      <c r="J30" s="23" t="str">
+      <c r="J30" s="24" t="str">
         <f t="array" ref="J30">INDEX(T28:T31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
         <v>🇵🇾 Paraguay</v>
       </c>
-      <c r="K30" s="22">
+      <c r="K30" s="23">
         <f t="array" ref="K30">INDEX(U28:U31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
         <v>3</v>
       </c>
-      <c r="L30" s="22">
+      <c r="L30" s="23">
         <f t="array" ref="L30">INDEX(V28:V31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
         <v>1</v>
       </c>
-      <c r="M30" s="22">
+      <c r="M30" s="23">
         <f t="array" ref="M30">INDEX(W28:W31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
-        <v>1</v>
-      </c>
-      <c r="N30" s="22">
+        <v>0</v>
+      </c>
+      <c r="N30" s="23">
         <f t="array" ref="N30">INDEX(X28:X31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
-        <v>1</v>
-      </c>
-      <c r="O30" s="22">
+        <v>2</v>
+      </c>
+      <c r="O30" s="23">
         <f t="array" ref="O30">INDEX(Y28:Y31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
-        <v>3</v>
-      </c>
-      <c r="P30" s="22">
+        <v>4</v>
+      </c>
+      <c r="P30" s="23">
         <f t="array" ref="P30">INDEX(Z28:Z31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
-        <v>3</v>
-      </c>
-      <c r="Q30" s="22">
+        <v>4</v>
+      </c>
+      <c r="Q30" s="23">
         <f t="array" ref="Q30">INDEX(AA28:AA31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
         <v>0</v>
       </c>
-      <c r="R30" s="22">
+      <c r="R30" s="23">
         <f t="array" ref="R30">INDEX(AB28:AB31,MATCH(LARGE(AC28:AC31,3),AC28:AC31,0))</f>
-        <v>4</v>
-      </c>
-      <c r="T30" s="21" t="str">
+        <v>3</v>
+      </c>
+      <c r="T30" s="22" t="str">
         <f>B29</f>
         <v>Australia 🇦🇺</v>
       </c>
-      <c r="U30" s="21">
+      <c r="U30" s="22">
         <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29)),1,0)+IF(AND(ISNUMBER(D30),ISNUMBER(E30)),1,0)+IF(AND(ISNUMBER(D33),ISNUMBER(E33)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V30" s="21">
+      <c r="V30" s="22">
         <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29),D29&gt;E29),1,0)+IF(AND(ISNUMBER(D30),ISNUMBER(E30),E30&gt;D30),1,0)+IF(AND(ISNUMBER(D33),ISNUMBER(E33),E33&gt;D33),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W30" s="21">
+      <c r="W30" s="22">
         <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29),D29=E29),1,0)+IF(AND(ISNUMBER(D30),ISNUMBER(E30),D30=E30),1,0)+IF(AND(ISNUMBER(D33),ISNUMBER(E33),D33=E33),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X30" s="21">
+      <c r="X30" s="22">
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="Y30" s="21">
+      <c r="Y30" s="22">
         <f>IF(ISNUMBER(D29),D29,0)+IF(ISNUMBER(E30),E30,0)+IF(ISNUMBER(E33),E33,0)</f>
         <v>1</v>
       </c>
-      <c r="Z30" s="21">
+      <c r="Z30" s="22">
         <f>IF(ISNUMBER(E29),E29,0)+IF(ISNUMBER(D30),D30,0)+IF(ISNUMBER(D33),D33,0)</f>
-        <v>5</v>
-      </c>
-      <c r="AA30" s="21">
+        <v>6</v>
+      </c>
+      <c r="AA30" s="22">
         <f t="shared" si="15"/>
-        <v>-4</v>
-      </c>
-      <c r="AB30" s="21">
+        <v>-5</v>
+      </c>
+      <c r="AB30" s="22">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AC30" s="21">
+      <c r="AC30" s="22">
         <f>AB30*1000000+(AA30+100)*1000+Y30*10+2</f>
-        <v>96012</v>
+        <v>95012</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -4088,96 +4100,96 @@
       <c r="C31" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>1.0</v>
       </c>
       <c r="E31" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="F31" s="17" t="s">
+        <v>2.0</v>
+      </c>
+      <c r="F31" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="G31" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="23">
         <v>4.0</v>
       </c>
-      <c r="J31" s="23" t="str">
+      <c r="J31" s="24" t="str">
         <f t="array" ref="J31">INDEX(T28:T31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
         <v>Australia 🇦🇺</v>
       </c>
-      <c r="K31" s="22">
+      <c r="K31" s="23">
         <f t="array" ref="K31">INDEX(U28:U31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
         <v>3</v>
       </c>
-      <c r="L31" s="22">
+      <c r="L31" s="23">
         <f t="array" ref="L31">INDEX(V28:V31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
         <v>0</v>
       </c>
-      <c r="M31" s="22">
+      <c r="M31" s="23">
         <f t="array" ref="M31">INDEX(W28:W31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
         <v>0</v>
       </c>
-      <c r="N31" s="22">
+      <c r="N31" s="23">
         <f t="array" ref="N31">INDEX(X28:X31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
         <v>3</v>
       </c>
-      <c r="O31" s="22">
+      <c r="O31" s="23">
         <f t="array" ref="O31">INDEX(Y28:Y31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
         <v>1</v>
       </c>
-      <c r="P31" s="22">
+      <c r="P31" s="23">
         <f t="array" ref="P31">INDEX(Z28:Z31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
-        <v>5</v>
-      </c>
-      <c r="Q31" s="22">
+        <v>6</v>
+      </c>
+      <c r="Q31" s="23">
         <f t="array" ref="Q31">INDEX(AA28:AA31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
-        <v>-4</v>
-      </c>
-      <c r="R31" s="22">
+        <v>-5</v>
+      </c>
+      <c r="R31" s="23">
         <f t="array" ref="R31">INDEX(AB28:AB31,MATCH(LARGE(AC28:AC31,4),AC28:AC31,0))</f>
         <v>0</v>
       </c>
-      <c r="T31" s="21" t="str">
+      <c r="T31" s="22" t="str">
         <f>F29</f>
         <v>🇹🇷 Turquía</v>
       </c>
-      <c r="U31" s="21">
+      <c r="U31" s="22">
         <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29)),1,0)+IF(AND(ISNUMBER(D31),ISNUMBER(E31)),1,0)+IF(AND(ISNUMBER(D32),ISNUMBER(E32)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V31" s="21">
+      <c r="V31" s="22">
         <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29),E29&gt;D29),1,0)+IF(AND(ISNUMBER(D31),ISNUMBER(E31),E31&gt;D31),1,0)+IF(AND(ISNUMBER(D32),ISNUMBER(E32),E32&gt;D32),1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="W31" s="22">
+        <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29),D29=E29),1,0)+IF(AND(ISNUMBER(D31),ISNUMBER(E31),D31=E31),1,0)+IF(AND(ISNUMBER(D32),ISNUMBER(E32),D32=E32),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W31" s="21">
-        <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29),D29=E29),1,0)+IF(AND(ISNUMBER(D31),ISNUMBER(E31),D31=E31),1,0)+IF(AND(ISNUMBER(D32),ISNUMBER(E32),D32=E32),1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="X31" s="21">
+      <c r="X31" s="22">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Y31" s="21">
+      <c r="Y31" s="22">
         <f>IF(ISNUMBER(E29),E29,0)+IF(ISNUMBER(E31),E31,0)+IF(ISNUMBER(E32),E32,0)</f>
-        <v>5</v>
-      </c>
-      <c r="Z31" s="21">
+        <v>6</v>
+      </c>
+      <c r="Z31" s="22">
         <f>IF(ISNUMBER(D29),D29,0)+IF(ISNUMBER(D31),D31,0)+IF(ISNUMBER(D32),D32,0)</f>
         <v>4</v>
       </c>
-      <c r="AA31" s="21">
+      <c r="AA31" s="22">
         <f t="shared" si="15"/>
-        <v>1</v>
-      </c>
-      <c r="AB31" s="21">
+        <v>2</v>
+      </c>
+      <c r="AB31" s="22">
         <f t="shared" si="16"/>
-        <v>5</v>
-      </c>
-      <c r="AC31" s="21">
+        <v>7</v>
+      </c>
+      <c r="AC31" s="22">
         <f>AB31*1000000+(AA31+100)*1000+Y31*10+1</f>
-        <v>5101051</v>
+        <v>7102061</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -4187,16 +4199,16 @@
       <c r="C32" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>2.0</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>2.0</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="19" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4208,20 +4220,20 @@
         <v>91</v>
       </c>
       <c r="D33" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="E33" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="E33" s="17">
         <v>0.0</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="34" ht="18.0" customHeight="1">
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C34" s="4"/>
@@ -4267,94 +4279,94 @@
       <c r="C35" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="17">
         <v>4.0</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="17">
         <v>0.0</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <v>1.0</v>
       </c>
-      <c r="J35" s="20" t="str">
+      <c r="J35" s="21" t="str">
         <f t="array" ref="J35">INDEX(T35:T38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>Alemania 🇩🇪</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="20">
         <f t="array" ref="K35">INDEX(U35:U38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>3</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="20">
         <f t="array" ref="L35">INDEX(V35:V38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>3</v>
       </c>
-      <c r="M35" s="19">
+      <c r="M35" s="20">
         <f t="array" ref="M35">INDEX(W35:W38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="N35" s="19">
+      <c r="N35" s="20">
         <f t="array" ref="N35">INDEX(X35:X38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="O35" s="19">
+      <c r="O35" s="20">
         <f t="array" ref="O35">INDEX(Y35:Y38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>9</v>
       </c>
-      <c r="P35" s="19">
+      <c r="P35" s="20">
         <f t="array" ref="P35">INDEX(Z35:Z38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>1</v>
       </c>
-      <c r="Q35" s="19">
+      <c r="Q35" s="20">
         <f t="array" ref="Q35">INDEX(AA35:AA38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>8</v>
       </c>
-      <c r="R35" s="19">
+      <c r="R35" s="20">
         <f t="array" ref="R35">INDEX(AB35:AB38,MATCH(LARGE(AC35:AC38,1),AC35:AC38,0))</f>
         <v>9</v>
       </c>
-      <c r="T35" s="21" t="str">
+      <c r="T35" s="22" t="str">
         <f>B35</f>
         <v>Alemania 🇩🇪</v>
       </c>
-      <c r="U35" s="21">
+      <c r="U35" s="22">
         <f>IF(AND(ISNUMBER(D35),ISNUMBER(E35)),1,0)+IF(AND(ISNUMBER(D37),ISNUMBER(E37)),1,0)+IF(AND(ISNUMBER(D39),ISNUMBER(E39)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V35" s="21">
+      <c r="V35" s="22">
         <f>IF(AND(ISNUMBER(D35),ISNUMBER(E35),D35&gt;E35),1,0)+IF(AND(ISNUMBER(D37),ISNUMBER(E37),D37&gt;E37),1,0)+IF(AND(ISNUMBER(D39),ISNUMBER(E39),D39&gt;E39),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W35" s="21">
+      <c r="W35" s="22">
         <f>IF(AND(ISNUMBER(D35),ISNUMBER(E35),D35=E35),1,0)+IF(AND(ISNUMBER(D37),ISNUMBER(E37),D37=E37),1,0)+IF(AND(ISNUMBER(D39),ISNUMBER(E39),D39=E39),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X35" s="21">
+      <c r="X35" s="22">
         <f t="shared" ref="X35:X38" si="18">U35-V35-W35</f>
         <v>0</v>
       </c>
-      <c r="Y35" s="21">
+      <c r="Y35" s="22">
         <f t="shared" ref="Y35:Z35" si="17">IF(ISNUMBER(D35),D35,0)+IF(ISNUMBER(D37),D37,0)+IF(ISNUMBER(D39),D39,0)</f>
         <v>9</v>
       </c>
-      <c r="Z35" s="21">
+      <c r="Z35" s="22">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="AA35" s="21">
+      <c r="AA35" s="22">
         <f t="shared" ref="AA35:AA38" si="19">Y35-Z35</f>
         <v>8</v>
       </c>
-      <c r="AB35" s="21">
+      <c r="AB35" s="22">
         <f t="shared" ref="AB35:AB38" si="20">V35*3+W35</f>
         <v>9</v>
       </c>
-      <c r="AC35" s="21">
+      <c r="AC35" s="22">
         <f>AB35*1000000+(AA35+100)*1000+Y35*10+4</f>
         <v>9108094</v>
       </c>
@@ -4366,96 +4378,96 @@
       <c r="C36" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="17">
         <v>0.0</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="17">
         <v>2.0</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <v>2.0</v>
       </c>
-      <c r="J36" s="20" t="str">
+      <c r="J36" s="21" t="str">
         <f t="array" ref="J36">INDEX(T35:T38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>🇪🇨 Ecuador</v>
       </c>
-      <c r="K36" s="19">
+      <c r="K36" s="20">
         <f t="array" ref="K36">INDEX(U35:U38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>3</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="20">
         <f t="array" ref="L36">INDEX(V35:V38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>2</v>
       </c>
-      <c r="M36" s="19">
+      <c r="M36" s="20">
         <f t="array" ref="M36">INDEX(W35:W38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="N36" s="19">
+      <c r="N36" s="20">
         <f t="array" ref="N36">INDEX(X35:X38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>1</v>
       </c>
-      <c r="O36" s="19">
+      <c r="O36" s="20">
         <f t="array" ref="O36">INDEX(Y35:Y38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>6</v>
       </c>
-      <c r="P36" s="19">
+      <c r="P36" s="20">
         <f t="array" ref="P36">INDEX(Z35:Z38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>2</v>
       </c>
-      <c r="Q36" s="19">
+      <c r="Q36" s="20">
         <f t="array" ref="Q36">INDEX(AA35:AA38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>4</v>
       </c>
-      <c r="R36" s="19">
+      <c r="R36" s="20">
         <f t="array" ref="R36">INDEX(AB35:AB38,MATCH(LARGE(AC35:AC38,2),AC35:AC38,0))</f>
         <v>6</v>
       </c>
-      <c r="T36" s="21" t="str">
+      <c r="T36" s="22" t="str">
         <f>F35</f>
         <v>🇨🇼 Curazao</v>
       </c>
-      <c r="U36" s="21">
+      <c r="U36" s="22">
         <f>IF(AND(ISNUMBER(D38),ISNUMBER(E38)),1,0)+IF(AND(ISNUMBER(D40),ISNUMBER(E40)),1,0)+IF(AND(ISNUMBER(D35),ISNUMBER(E35)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V36" s="21">
+      <c r="V36" s="22">
         <f>IF(AND(ISNUMBER(D38),ISNUMBER(E38),D38&gt;E38),1,0)+IF(AND(ISNUMBER(D40),ISNUMBER(E40),D40&gt;E40),1,0)+IF(AND(ISNUMBER(D35),ISNUMBER(E35),E35&gt;D35),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W36" s="21">
+      <c r="W36" s="22">
         <f>IF(AND(ISNUMBER(D38),ISNUMBER(E38),D38=E38),1,0)+IF(AND(ISNUMBER(D40),ISNUMBER(E40),D40=E40),1,0)+IF(AND(ISNUMBER(D35),ISNUMBER(E35),D35=E35),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X36" s="21">
+      <c r="X36" s="22">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
-      <c r="Y36" s="21">
+      <c r="Y36" s="22">
         <f>IF(ISNUMBER(D38),D38,0)+IF(ISNUMBER(D40),D40,0)+IF(ISNUMBER(E35),E35,0)</f>
         <v>0</v>
       </c>
-      <c r="Z36" s="21">
+      <c r="Z36" s="22">
         <f>IF(ISNUMBER(E38),E38,0)+IF(ISNUMBER(E40),E40,0)+IF(ISNUMBER(D35),D35,0)</f>
-        <v>8</v>
-      </c>
-      <c r="AA36" s="21">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="22">
         <f t="shared" si="19"/>
-        <v>-8</v>
-      </c>
-      <c r="AB36" s="21">
+        <v>-9</v>
+      </c>
+      <c r="AB36" s="22">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AC36" s="21">
+      <c r="AC36" s="22">
         <f>AB36*1000000+(AA36+100)*1000+Y36*10+3</f>
-        <v>92003</v>
+        <v>91003</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -4465,96 +4477,96 @@
       <c r="C37" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="17">
         <v>3.0</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="17">
         <v>0.0</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="I37" s="22">
+      <c r="I37" s="23">
         <v>3.0</v>
       </c>
-      <c r="J37" s="23" t="str">
+      <c r="J37" s="24" t="str">
         <f t="array" ref="J37">INDEX(T35:T38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
         <v>Costa Rica 🇨🇷</v>
       </c>
-      <c r="K37" s="22">
+      <c r="K37" s="23">
         <f t="array" ref="K37">INDEX(U35:U38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
         <v>3</v>
       </c>
-      <c r="L37" s="22">
+      <c r="L37" s="23">
         <f t="array" ref="L37">INDEX(V35:V38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
         <v>1</v>
       </c>
-      <c r="M37" s="22">
+      <c r="M37" s="23">
         <f t="array" ref="M37">INDEX(W35:W38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="N37" s="22">
+      <c r="N37" s="23">
         <f t="array" ref="N37">INDEX(X35:X38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
         <v>2</v>
       </c>
-      <c r="O37" s="22">
+      <c r="O37" s="23">
         <f t="array" ref="O37">INDEX(Y35:Y38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
-        <v>1</v>
-      </c>
-      <c r="P37" s="22">
+        <v>2</v>
+      </c>
+      <c r="P37" s="23">
         <f t="array" ref="P37">INDEX(Z35:Z38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
         <v>5</v>
       </c>
-      <c r="Q37" s="22">
+      <c r="Q37" s="23">
         <f t="array" ref="Q37">INDEX(AA35:AA38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
-        <v>-4</v>
-      </c>
-      <c r="R37" s="22">
+        <v>-3</v>
+      </c>
+      <c r="R37" s="23">
         <f t="array" ref="R37">INDEX(AB35:AB38,MATCH(LARGE(AC35:AC38,3),AC35:AC38,0))</f>
         <v>3</v>
       </c>
-      <c r="T37" s="21" t="str">
+      <c r="T37" s="22" t="str">
         <f>B36</f>
         <v>Costa Rica 🇨🇷</v>
       </c>
-      <c r="U37" s="21">
+      <c r="U37" s="22">
         <f>IF(AND(ISNUMBER(D36),ISNUMBER(E36)),1,0)+IF(AND(ISNUMBER(D37),ISNUMBER(E37)),1,0)+IF(AND(ISNUMBER(D40),ISNUMBER(E40)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V37" s="21">
+      <c r="V37" s="22">
         <f>IF(AND(ISNUMBER(D36),ISNUMBER(E36),D36&gt;E36),1,0)+IF(AND(ISNUMBER(D37),ISNUMBER(E37),E37&gt;D37),1,0)+IF(AND(ISNUMBER(D40),ISNUMBER(E40),E40&gt;D40),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W37" s="21">
+      <c r="W37" s="22">
         <f>IF(AND(ISNUMBER(D36),ISNUMBER(E36),D36=E36),1,0)+IF(AND(ISNUMBER(D37),ISNUMBER(E37),D37=E37),1,0)+IF(AND(ISNUMBER(D40),ISNUMBER(E40),D40=E40),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X37" s="21">
+      <c r="X37" s="22">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
-      <c r="Y37" s="21">
+      <c r="Y37" s="22">
         <f>IF(ISNUMBER(D36),D36,0)+IF(ISNUMBER(E37),E37,0)+IF(ISNUMBER(E40),E40,0)</f>
-        <v>1</v>
-      </c>
-      <c r="Z37" s="21">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="22">
         <f>IF(ISNUMBER(E36),E36,0)+IF(ISNUMBER(D37),D37,0)+IF(ISNUMBER(D40),D40,0)</f>
         <v>5</v>
       </c>
-      <c r="AA37" s="21">
+      <c r="AA37" s="22">
         <f t="shared" si="19"/>
-        <v>-4</v>
-      </c>
-      <c r="AB37" s="21">
+        <v>-3</v>
+      </c>
+      <c r="AB37" s="22">
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
-      <c r="AC37" s="21">
+      <c r="AC37" s="22">
         <f>AB37*1000000+(AA37+100)*1000+Y37*10+2</f>
-        <v>3096012</v>
+        <v>3097022</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -4564,94 +4576,94 @@
       <c r="C38" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="17">
         <v>0.0</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="17">
         <v>3.0</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="I38" s="22">
+      <c r="I38" s="23">
         <v>4.0</v>
       </c>
-      <c r="J38" s="23" t="str">
+      <c r="J38" s="24" t="str">
         <f t="array" ref="J38">INDEX(T35:T38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
         <v>🇨🇼 Curazao</v>
       </c>
-      <c r="K38" s="22">
+      <c r="K38" s="23">
         <f t="array" ref="K38">INDEX(U35:U38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
         <v>3</v>
       </c>
-      <c r="L38" s="22">
+      <c r="L38" s="23">
         <f t="array" ref="L38">INDEX(V35:V38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="M38" s="22">
+      <c r="M38" s="23">
         <f t="array" ref="M38">INDEX(W35:W38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="N38" s="22">
+      <c r="N38" s="23">
         <f t="array" ref="N38">INDEX(X35:X38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
         <v>3</v>
       </c>
-      <c r="O38" s="22">
+      <c r="O38" s="23">
         <f t="array" ref="O38">INDEX(Y35:Y38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="P38" s="22">
+      <c r="P38" s="23">
         <f t="array" ref="P38">INDEX(Z35:Z38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
-        <v>8</v>
-      </c>
-      <c r="Q38" s="22">
+        <v>9</v>
+      </c>
+      <c r="Q38" s="23">
         <f t="array" ref="Q38">INDEX(AA35:AA38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
-        <v>-8</v>
-      </c>
-      <c r="R38" s="22">
+        <v>-9</v>
+      </c>
+      <c r="R38" s="23">
         <f t="array" ref="R38">INDEX(AB35:AB38,MATCH(LARGE(AC35:AC38,4),AC35:AC38,0))</f>
         <v>0</v>
       </c>
-      <c r="T38" s="21" t="str">
+      <c r="T38" s="22" t="str">
         <f>F36</f>
         <v>🇪🇨 Ecuador</v>
       </c>
-      <c r="U38" s="21">
+      <c r="U38" s="22">
         <f>IF(AND(ISNUMBER(D36),ISNUMBER(E36)),1,0)+IF(AND(ISNUMBER(D38),ISNUMBER(E38)),1,0)+IF(AND(ISNUMBER(D39),ISNUMBER(E39)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V38" s="21">
+      <c r="V38" s="22">
         <f>IF(AND(ISNUMBER(D36),ISNUMBER(E36),E36&gt;D36),1,0)+IF(AND(ISNUMBER(D38),ISNUMBER(E38),E38&gt;D38),1,0)+IF(AND(ISNUMBER(D39),ISNUMBER(E39),E39&gt;D39),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W38" s="21">
+      <c r="W38" s="22">
         <f>IF(AND(ISNUMBER(D36),ISNUMBER(E36),D36=E36),1,0)+IF(AND(ISNUMBER(D38),ISNUMBER(E38),D38=E38),1,0)+IF(AND(ISNUMBER(D39),ISNUMBER(E39),D39=E39),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X38" s="21">
+      <c r="X38" s="22">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="Y38" s="21">
+      <c r="Y38" s="22">
         <f>IF(ISNUMBER(E36),E36,0)+IF(ISNUMBER(E38),E38,0)+IF(ISNUMBER(E39),E39,0)</f>
         <v>6</v>
       </c>
-      <c r="Z38" s="21">
+      <c r="Z38" s="22">
         <f>IF(ISNUMBER(D36),D36,0)+IF(ISNUMBER(D38),D38,0)+IF(ISNUMBER(D39),D39,0)</f>
         <v>2</v>
       </c>
-      <c r="AA38" s="21">
+      <c r="AA38" s="22">
         <f t="shared" si="19"/>
         <v>4</v>
       </c>
-      <c r="AB38" s="21">
+      <c r="AB38" s="22">
         <f t="shared" si="20"/>
         <v>6</v>
       </c>
-      <c r="AC38" s="21">
+      <c r="AC38" s="22">
         <f>AB38*1000000+(AA38+100)*1000+Y38*10+1</f>
         <v>6104061</v>
       </c>
@@ -4663,16 +4675,16 @@
       <c r="C39" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="17">
         <v>2.0</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="17">
         <v>1.0</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="19" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4683,21 +4695,21 @@
       <c r="C40" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="17">
         <v>0.0</v>
       </c>
       <c r="E40" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="F40" s="17" t="s">
+        <v>2.0</v>
+      </c>
+      <c r="F40" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="19" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="41" ht="18.0" customHeight="1">
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="25" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="4"/>
@@ -4743,94 +4755,94 @@
       <c r="C42" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="17">
         <v>2.0</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="17">
         <v>1.0</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="20">
         <v>1.0</v>
       </c>
-      <c r="J42" s="20" t="str">
+      <c r="J42" s="21" t="str">
         <f t="array" ref="J42">INDEX(T42:T45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>Países Bajos 🇳🇱</v>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="20">
         <f t="array" ref="K42">INDEX(U42:U45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="20">
         <f t="array" ref="L42">INDEX(V42:V45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="M42" s="19">
+      <c r="M42" s="20">
         <f t="array" ref="M42">INDEX(W42:W45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="N42" s="19">
+      <c r="N42" s="20">
         <f t="array" ref="N42">INDEX(X42:X45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="O42" s="19">
+      <c r="O42" s="20">
         <f t="array" ref="O42">INDEX(Y42:Y45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>7</v>
       </c>
-      <c r="P42" s="19">
+      <c r="P42" s="20">
         <f t="array" ref="P42">INDEX(Z42:Z45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>1</v>
       </c>
-      <c r="Q42" s="19">
+      <c r="Q42" s="20">
         <f t="array" ref="Q42">INDEX(AA42:AA45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>6</v>
       </c>
-      <c r="R42" s="19">
+      <c r="R42" s="20">
         <f t="array" ref="R42">INDEX(AB42:AB45,MATCH(LARGE(AC42:AC45,1),AC42:AC45,0))</f>
         <v>9</v>
       </c>
-      <c r="T42" s="21" t="str">
+      <c r="T42" s="22" t="str">
         <f>B42</f>
         <v>Países Bajos 🇳🇱</v>
       </c>
-      <c r="U42" s="21">
+      <c r="U42" s="22">
         <f>IF(AND(ISNUMBER(D42),ISNUMBER(E42)),1,0)+IF(AND(ISNUMBER(D44),ISNUMBER(E44)),1,0)+IF(AND(ISNUMBER(D46),ISNUMBER(E46)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V42" s="21">
+      <c r="V42" s="22">
         <f>IF(AND(ISNUMBER(D42),ISNUMBER(E42),D42&gt;E42),1,0)+IF(AND(ISNUMBER(D44),ISNUMBER(E44),D44&gt;E44),1,0)+IF(AND(ISNUMBER(D46),ISNUMBER(E46),D46&gt;E46),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W42" s="21">
+      <c r="W42" s="22">
         <f>IF(AND(ISNUMBER(D42),ISNUMBER(E42),D42=E42),1,0)+IF(AND(ISNUMBER(D44),ISNUMBER(E44),D44=E44),1,0)+IF(AND(ISNUMBER(D46),ISNUMBER(E46),D46=E46),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X42" s="21">
+      <c r="X42" s="22">
         <f t="shared" ref="X42:X45" si="22">U42-V42-W42</f>
         <v>0</v>
       </c>
-      <c r="Y42" s="21">
+      <c r="Y42" s="22">
         <f t="shared" ref="Y42:Z42" si="21">IF(ISNUMBER(D42),D42,0)+IF(ISNUMBER(D44),D44,0)+IF(ISNUMBER(D46),D46,0)</f>
         <v>7</v>
       </c>
-      <c r="Z42" s="21">
+      <c r="Z42" s="22">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="AA42" s="21">
+      <c r="AA42" s="22">
         <f t="shared" ref="AA42:AA45" si="23">Y42-Z42</f>
         <v>6</v>
       </c>
-      <c r="AB42" s="21">
+      <c r="AB42" s="22">
         <f t="shared" ref="AB42:AB45" si="24">V42*3+W42</f>
         <v>9</v>
       </c>
-      <c r="AC42" s="21">
+      <c r="AC42" s="22">
         <f>AB42*1000000+(AA42+100)*1000+Y42*10+4</f>
         <v>9106074</v>
       </c>
@@ -4842,94 +4854,94 @@
       <c r="C43" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="17">
         <v>0.0</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="17">
         <v>1.0</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G43" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="20">
         <v>2.0</v>
       </c>
-      <c r="J43" s="20" t="str">
+      <c r="J43" s="21" t="str">
         <f t="array" ref="J43">INDEX(T42:T45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>🇯🇵 Japón</v>
       </c>
-      <c r="K43" s="19">
+      <c r="K43" s="20">
         <f t="array" ref="K43">INDEX(U42:U45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="20">
         <f t="array" ref="L43">INDEX(V42:V45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>2</v>
       </c>
-      <c r="M43" s="19">
+      <c r="M43" s="20">
         <f t="array" ref="M43">INDEX(W42:W45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="N43" s="19">
+      <c r="N43" s="20">
         <f t="array" ref="N43">INDEX(X42:X45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>1</v>
       </c>
-      <c r="O43" s="19">
+      <c r="O43" s="20">
         <f t="array" ref="O43">INDEX(Y42:Y45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>5</v>
       </c>
-      <c r="P43" s="19">
+      <c r="P43" s="20">
         <f t="array" ref="P43">INDEX(Z42:Z45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="Q43" s="19">
+      <c r="Q43" s="20">
         <f t="array" ref="Q43">INDEX(AA42:AA45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>2</v>
       </c>
-      <c r="R43" s="19">
+      <c r="R43" s="20">
         <f t="array" ref="R43">INDEX(AB42:AB45,MATCH(LARGE(AC42:AC45,2),AC42:AC45,0))</f>
         <v>6</v>
       </c>
-      <c r="T43" s="21" t="str">
+      <c r="T43" s="22" t="str">
         <f>F42</f>
         <v>🇯🇵 Japón</v>
       </c>
-      <c r="U43" s="21">
+      <c r="U43" s="22">
         <f>IF(AND(ISNUMBER(D45),ISNUMBER(E45)),1,0)+IF(AND(ISNUMBER(D47),ISNUMBER(E47)),1,0)+IF(AND(ISNUMBER(D42),ISNUMBER(E42)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V43" s="21">
+      <c r="V43" s="22">
         <f>IF(AND(ISNUMBER(D45),ISNUMBER(E45),D45&gt;E45),1,0)+IF(AND(ISNUMBER(D47),ISNUMBER(E47),D47&gt;E47),1,0)+IF(AND(ISNUMBER(D42),ISNUMBER(E42),E42&gt;D42),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W43" s="21">
+      <c r="W43" s="22">
         <f>IF(AND(ISNUMBER(D45),ISNUMBER(E45),D45=E45),1,0)+IF(AND(ISNUMBER(D47),ISNUMBER(E47),D47=E47),1,0)+IF(AND(ISNUMBER(D42),ISNUMBER(E42),D42=E42),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X43" s="21">
+      <c r="X43" s="22">
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
-      <c r="Y43" s="21">
+      <c r="Y43" s="22">
         <f>IF(ISNUMBER(D45),D45,0)+IF(ISNUMBER(D47),D47,0)+IF(ISNUMBER(E42),E42,0)</f>
         <v>5</v>
       </c>
-      <c r="Z43" s="21">
+      <c r="Z43" s="22">
         <f>IF(ISNUMBER(E45),E45,0)+IF(ISNUMBER(E47),E47,0)+IF(ISNUMBER(D42),D42,0)</f>
         <v>3</v>
       </c>
-      <c r="AA43" s="21">
+      <c r="AA43" s="22">
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
-      <c r="AB43" s="21">
+      <c r="AB43" s="22">
         <f t="shared" si="24"/>
         <v>6</v>
       </c>
-      <c r="AC43" s="21">
+      <c r="AC43" s="22">
         <f>AB43*1000000+(AA43+100)*1000+Y43*10+3</f>
         <v>6102053</v>
       </c>
@@ -4941,94 +4953,94 @@
       <c r="C44" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="17">
         <v>3.0</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="17">
         <v>0.0</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="G44" s="18" t="s">
+      <c r="G44" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="23">
         <v>3.0</v>
       </c>
-      <c r="J44" s="23" t="str">
+      <c r="J44" s="24" t="str">
         <f t="array" ref="J44">INDEX(T42:T45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>🇸🇪 Suecia</v>
       </c>
-      <c r="K44" s="22">
+      <c r="K44" s="23">
         <f t="array" ref="K44">INDEX(U42:U45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="L44" s="22">
+      <c r="L44" s="23">
         <f t="array" ref="L44">INDEX(V42:V45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>1</v>
       </c>
-      <c r="M44" s="22">
+      <c r="M44" s="23">
         <f t="array" ref="M44">INDEX(W42:W45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="N44" s="22">
+      <c r="N44" s="23">
         <f t="array" ref="N44">INDEX(X42:X45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>2</v>
       </c>
-      <c r="O44" s="22">
+      <c r="O44" s="23">
         <f t="array" ref="O44">INDEX(Y42:Y45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>2</v>
       </c>
-      <c r="P44" s="22">
+      <c r="P44" s="23">
         <f t="array" ref="P44">INDEX(Z42:Z45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>4</v>
       </c>
-      <c r="Q44" s="22">
+      <c r="Q44" s="23">
         <f t="array" ref="Q44">INDEX(AA42:AA45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>-2</v>
       </c>
-      <c r="R44" s="22">
+      <c r="R44" s="23">
         <f t="array" ref="R44">INDEX(AB42:AB45,MATCH(LARGE(AC42:AC45,3),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="T44" s="21" t="str">
+      <c r="T44" s="22" t="str">
         <f>B43</f>
         <v>Túnez 🇹🇳</v>
       </c>
-      <c r="U44" s="21">
+      <c r="U44" s="22">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43)),1,0)+IF(AND(ISNUMBER(D44),ISNUMBER(E44)),1,0)+IF(AND(ISNUMBER(D47),ISNUMBER(E47)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V44" s="21">
+      <c r="V44" s="22">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43),D43&gt;E43),1,0)+IF(AND(ISNUMBER(D44),ISNUMBER(E44),E44&gt;D44),1,0)+IF(AND(ISNUMBER(D47),ISNUMBER(E47),E47&gt;D47),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W44" s="21">
+      <c r="W44" s="22">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43),D43=E43),1,0)+IF(AND(ISNUMBER(D44),ISNUMBER(E44),D44=E44),1,0)+IF(AND(ISNUMBER(D47),ISNUMBER(E47),D47=E47),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X44" s="21">
+      <c r="X44" s="22">
         <f t="shared" si="22"/>
         <v>3</v>
       </c>
-      <c r="Y44" s="21">
+      <c r="Y44" s="22">
         <f>IF(ISNUMBER(D43),D43,0)+IF(ISNUMBER(E44),E44,0)+IF(ISNUMBER(E47),E47,0)</f>
         <v>0</v>
       </c>
-      <c r="Z44" s="21">
+      <c r="Z44" s="22">
         <f>IF(ISNUMBER(E43),E43,0)+IF(ISNUMBER(D44),D44,0)+IF(ISNUMBER(D47),D47,0)</f>
         <v>6</v>
       </c>
-      <c r="AA44" s="21">
+      <c r="AA44" s="22">
         <f t="shared" si="23"/>
         <v>-6</v>
       </c>
-      <c r="AB44" s="21">
+      <c r="AB44" s="22">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AC44" s="21">
+      <c r="AC44" s="22">
         <f>AB44*1000000+(AA44+100)*1000+Y44*10+2</f>
         <v>94002</v>
       </c>
@@ -5040,94 +5052,94 @@
       <c r="C45" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="17">
         <v>2.0</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="17">
         <v>1.0</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="18" t="s">
+      <c r="G45" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="23">
         <v>4.0</v>
       </c>
-      <c r="J45" s="23" t="str">
+      <c r="J45" s="24" t="str">
         <f t="array" ref="J45">INDEX(T42:T45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>Túnez 🇹🇳</v>
       </c>
-      <c r="K45" s="22">
+      <c r="K45" s="23">
         <f t="array" ref="K45">INDEX(U42:U45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="L45" s="22">
+      <c r="L45" s="23">
         <f t="array" ref="L45">INDEX(V42:V45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="M45" s="22">
+      <c r="M45" s="23">
         <f t="array" ref="M45">INDEX(W42:W45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="N45" s="22">
+      <c r="N45" s="23">
         <f t="array" ref="N45">INDEX(X42:X45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>3</v>
       </c>
-      <c r="O45" s="22">
+      <c r="O45" s="23">
         <f t="array" ref="O45">INDEX(Y42:Y45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="P45" s="22">
+      <c r="P45" s="23">
         <f t="array" ref="P45">INDEX(Z42:Z45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>6</v>
       </c>
-      <c r="Q45" s="22">
+      <c r="Q45" s="23">
         <f t="array" ref="Q45">INDEX(AA42:AA45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>-6</v>
       </c>
-      <c r="R45" s="22">
+      <c r="R45" s="23">
         <f t="array" ref="R45">INDEX(AB42:AB45,MATCH(LARGE(AC42:AC45,4),AC42:AC45,0))</f>
         <v>0</v>
       </c>
-      <c r="T45" s="21" t="str">
+      <c r="T45" s="22" t="str">
         <f>F43</f>
         <v>🇸🇪 Suecia</v>
       </c>
-      <c r="U45" s="21">
+      <c r="U45" s="22">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43)),1,0)+IF(AND(ISNUMBER(D45),ISNUMBER(E45)),1,0)+IF(AND(ISNUMBER(D46),ISNUMBER(E46)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V45" s="21">
+      <c r="V45" s="22">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43),E43&gt;D43),1,0)+IF(AND(ISNUMBER(D45),ISNUMBER(E45),E45&gt;D45),1,0)+IF(AND(ISNUMBER(D46),ISNUMBER(E46),E46&gt;D46),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W45" s="21">
+      <c r="W45" s="22">
         <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43),D43=E43),1,0)+IF(AND(ISNUMBER(D45),ISNUMBER(E45),D45=E45),1,0)+IF(AND(ISNUMBER(D46),ISNUMBER(E46),D46=E46),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X45" s="21">
+      <c r="X45" s="22">
         <f t="shared" si="22"/>
         <v>2</v>
       </c>
-      <c r="Y45" s="21">
+      <c r="Y45" s="22">
         <f>IF(ISNUMBER(E43),E43,0)+IF(ISNUMBER(E45),E45,0)+IF(ISNUMBER(E46),E46,0)</f>
         <v>2</v>
       </c>
-      <c r="Z45" s="21">
+      <c r="Z45" s="22">
         <f>IF(ISNUMBER(D43),D43,0)+IF(ISNUMBER(D45),D45,0)+IF(ISNUMBER(D46),D46,0)</f>
         <v>4</v>
       </c>
-      <c r="AA45" s="21">
+      <c r="AA45" s="22">
         <f t="shared" si="23"/>
         <v>-2</v>
       </c>
-      <c r="AB45" s="21">
+      <c r="AB45" s="22">
         <f t="shared" si="24"/>
         <v>3</v>
       </c>
-      <c r="AC45" s="21">
+      <c r="AC45" s="22">
         <f>AB45*1000000+(AA45+100)*1000+Y45*10+1</f>
         <v>3098021</v>
       </c>
@@ -5139,16 +5151,16 @@
       <c r="C46" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="17">
         <v>2.0</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="17">
         <v>0.0</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="G46" s="18" t="s">
+      <c r="G46" s="19" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5159,21 +5171,21 @@
       <c r="C47" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="17">
         <v>2.0</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="17">
         <v>0.0</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="19" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="48" ht="18.0" customHeight="1">
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C48" s="4"/>
@@ -5219,96 +5231,96 @@
       <c r="C49" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="17">
         <v>2.0</v>
       </c>
       <c r="E49" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="I49" s="20">
         <v>1.0</v>
       </c>
-      <c r="F49" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="I49" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="J49" s="20" t="str">
+      <c r="J49" s="21" t="str">
         <f t="array" ref="J49">INDEX(T49:T52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
         <v>Bélgica 🇧🇪</v>
       </c>
-      <c r="K49" s="19">
+      <c r="K49" s="20">
         <f t="array" ref="K49">INDEX(U49:U52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
         <v>3</v>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="20">
         <f t="array" ref="L49">INDEX(V49:V52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
         <v>3</v>
       </c>
-      <c r="M49" s="19">
+      <c r="M49" s="20">
         <f t="array" ref="M49">INDEX(W49:W52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
         <v>0</v>
       </c>
-      <c r="N49" s="19">
+      <c r="N49" s="20">
         <f t="array" ref="N49">INDEX(X49:X52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
         <v>0</v>
       </c>
-      <c r="O49" s="19">
+      <c r="O49" s="20">
         <f t="array" ref="O49">INDEX(Y49:Y52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
         <v>7</v>
       </c>
-      <c r="P49" s="19">
+      <c r="P49" s="20">
         <f t="array" ref="P49">INDEX(Z49:Z52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q49" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="20">
         <f t="array" ref="Q49">INDEX(AA49:AA52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
-        <v>6</v>
-      </c>
-      <c r="R49" s="19">
+        <v>7</v>
+      </c>
+      <c r="R49" s="20">
         <f t="array" ref="R49">INDEX(AB49:AB52,MATCH(LARGE(AC49:AC52,1),AC49:AC52,0))</f>
         <v>9</v>
       </c>
-      <c r="T49" s="21" t="str">
+      <c r="T49" s="22" t="str">
         <f>B49</f>
         <v>Bélgica 🇧🇪</v>
       </c>
-      <c r="U49" s="21">
+      <c r="U49" s="22">
         <f>IF(AND(ISNUMBER(D49),ISNUMBER(E49)),1,0)+IF(AND(ISNUMBER(D51),ISNUMBER(E51)),1,0)+IF(AND(ISNUMBER(D53),ISNUMBER(E53)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V49" s="21">
+      <c r="V49" s="22">
         <f>IF(AND(ISNUMBER(D49),ISNUMBER(E49),D49&gt;E49),1,0)+IF(AND(ISNUMBER(D51),ISNUMBER(E51),D51&gt;E51),1,0)+IF(AND(ISNUMBER(D53),ISNUMBER(E53),D53&gt;E53),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W49" s="21">
+      <c r="W49" s="22">
         <f>IF(AND(ISNUMBER(D49),ISNUMBER(E49),D49=E49),1,0)+IF(AND(ISNUMBER(D51),ISNUMBER(E51),D51=E51),1,0)+IF(AND(ISNUMBER(D53),ISNUMBER(E53),D53=E53),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X49" s="21">
+      <c r="X49" s="22">
         <f t="shared" ref="X49:X52" si="26">U49-V49-W49</f>
         <v>0</v>
       </c>
-      <c r="Y49" s="21">
+      <c r="Y49" s="22">
         <f t="shared" ref="Y49:Z49" si="25">IF(ISNUMBER(D49),D49,0)+IF(ISNUMBER(D51),D51,0)+IF(ISNUMBER(D53),D53,0)</f>
         <v>7</v>
       </c>
-      <c r="Z49" s="21">
+      <c r="Z49" s="22">
         <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="AA49" s="21">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="22">
         <f t="shared" ref="AA49:AA52" si="27">Y49-Z49</f>
-        <v>6</v>
-      </c>
-      <c r="AB49" s="21">
+        <v>7</v>
+      </c>
+      <c r="AB49" s="22">
         <f t="shared" ref="AB49:AB52" si="28">V49*3+W49</f>
         <v>9</v>
       </c>
-      <c r="AC49" s="21">
+      <c r="AC49" s="22">
         <f>AB49*1000000+(AA49+100)*1000+Y49*10+4</f>
-        <v>9106074</v>
+        <v>9107074</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -5318,96 +5330,96 @@
       <c r="C50" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="17">
         <v>1.0</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="17">
         <v>0.0</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F50" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G50" s="18" t="s">
+      <c r="G50" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="I50" s="19">
+      <c r="I50" s="20">
         <v>2.0</v>
       </c>
-      <c r="J50" s="20" t="str">
+      <c r="J50" s="21" t="str">
         <f t="array" ref="J50">INDEX(T49:T52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
         <v>🇪🇬 Egipto</v>
       </c>
-      <c r="K50" s="19">
+      <c r="K50" s="20">
         <f t="array" ref="K50">INDEX(U49:U52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
         <v>3</v>
       </c>
-      <c r="L50" s="19">
+      <c r="L50" s="20">
         <f t="array" ref="L50">INDEX(V49:V52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
         <v>1</v>
       </c>
-      <c r="M50" s="19">
+      <c r="M50" s="20">
         <f t="array" ref="M50">INDEX(W49:W52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
         <v>1</v>
       </c>
-      <c r="N50" s="19">
+      <c r="N50" s="20">
         <f t="array" ref="N50">INDEX(X49:X52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
         <v>1</v>
       </c>
-      <c r="O50" s="19">
+      <c r="O50" s="20">
         <f t="array" ref="O50">INDEX(Y49:Y52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
+        <v>3</v>
+      </c>
+      <c r="P50" s="20">
+        <f t="array" ref="P50">INDEX(Z49:Z52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
         <v>4</v>
       </c>
-      <c r="P50" s="19">
-        <f t="array" ref="P50">INDEX(Z49:Z52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
-        <v>3</v>
-      </c>
-      <c r="Q50" s="19">
+      <c r="Q50" s="20">
         <f t="array" ref="Q50">INDEX(AA49:AA52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
-        <v>1</v>
-      </c>
-      <c r="R50" s="19">
+        <v>-1</v>
+      </c>
+      <c r="R50" s="20">
         <f t="array" ref="R50">INDEX(AB49:AB52,MATCH(LARGE(AC49:AC52,2),AC49:AC52,0))</f>
         <v>4</v>
       </c>
-      <c r="T50" s="21" t="str">
+      <c r="T50" s="22" t="str">
         <f>F49</f>
         <v>🇪🇬 Egipto</v>
       </c>
-      <c r="U50" s="21">
+      <c r="U50" s="22">
         <f>IF(AND(ISNUMBER(D52),ISNUMBER(E52)),1,0)+IF(AND(ISNUMBER(D54),ISNUMBER(E54)),1,0)+IF(AND(ISNUMBER(D49),ISNUMBER(E49)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V50" s="21">
+      <c r="V50" s="22">
         <f>IF(AND(ISNUMBER(D52),ISNUMBER(E52),D52&gt;E52),1,0)+IF(AND(ISNUMBER(D54),ISNUMBER(E54),D54&gt;E54),1,0)+IF(AND(ISNUMBER(D49),ISNUMBER(E49),E49&gt;D49),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W50" s="21">
+      <c r="W50" s="22">
         <f>IF(AND(ISNUMBER(D52),ISNUMBER(E52),D52=E52),1,0)+IF(AND(ISNUMBER(D54),ISNUMBER(E54),D54=E54),1,0)+IF(AND(ISNUMBER(D49),ISNUMBER(E49),D49=E49),1,0)</f>
         <v>1</v>
       </c>
-      <c r="X50" s="21">
+      <c r="X50" s="22">
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
-      <c r="Y50" s="21">
+      <c r="Y50" s="22">
         <f>IF(ISNUMBER(D52),D52,0)+IF(ISNUMBER(D54),D54,0)+IF(ISNUMBER(E49),E49,0)</f>
+        <v>3</v>
+      </c>
+      <c r="Z50" s="22">
+        <f>IF(ISNUMBER(E52),E52,0)+IF(ISNUMBER(E54),E54,0)+IF(ISNUMBER(D49),D49,0)</f>
         <v>4</v>
       </c>
-      <c r="Z50" s="21">
-        <f>IF(ISNUMBER(E52),E52,0)+IF(ISNUMBER(E54),E54,0)+IF(ISNUMBER(D49),D49,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA50" s="21">
+      <c r="AA50" s="22">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="AB50" s="21">
+        <v>-1</v>
+      </c>
+      <c r="AB50" s="22">
         <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AC50" s="21">
+      <c r="AC50" s="22">
         <f>AB50*1000000+(AA50+100)*1000+Y50*10+3</f>
-        <v>4101043</v>
+        <v>4099033</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
@@ -5417,94 +5429,94 @@
       <c r="C51" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="17">
         <v>2.0</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="17">
         <v>0.0</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="G51" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I51" s="22">
+      <c r="I51" s="23">
         <v>3.0</v>
       </c>
-      <c r="J51" s="23" t="str">
+      <c r="J51" s="24" t="str">
         <f t="array" ref="J51">INDEX(T49:T52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>Irán 🇮🇷</v>
       </c>
-      <c r="K51" s="22">
+      <c r="K51" s="23">
         <f t="array" ref="K51">INDEX(U49:U52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>3</v>
       </c>
-      <c r="L51" s="22">
+      <c r="L51" s="23">
         <f t="array" ref="L51">INDEX(V49:V52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>1</v>
       </c>
-      <c r="M51" s="22">
+      <c r="M51" s="23">
         <f t="array" ref="M51">INDEX(W49:W52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>1</v>
       </c>
-      <c r="N51" s="22">
+      <c r="N51" s="23">
         <f t="array" ref="N51">INDEX(X49:X52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>1</v>
       </c>
-      <c r="O51" s="22">
+      <c r="O51" s="23">
         <f t="array" ref="O51">INDEX(Y49:Y52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>2</v>
       </c>
-      <c r="P51" s="22">
+      <c r="P51" s="23">
         <f t="array" ref="P51">INDEX(Z49:Z52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>3</v>
       </c>
-      <c r="Q51" s="22">
+      <c r="Q51" s="23">
         <f t="array" ref="Q51">INDEX(AA49:AA52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>-1</v>
       </c>
-      <c r="R51" s="22">
+      <c r="R51" s="23">
         <f t="array" ref="R51">INDEX(AB49:AB52,MATCH(LARGE(AC49:AC52,3),AC49:AC52,0))</f>
         <v>4</v>
       </c>
-      <c r="T51" s="21" t="str">
+      <c r="T51" s="22" t="str">
         <f>B50</f>
         <v>Irán 🇮🇷</v>
       </c>
-      <c r="U51" s="21">
+      <c r="U51" s="22">
         <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50)),1,0)+IF(AND(ISNUMBER(D51),ISNUMBER(E51)),1,0)+IF(AND(ISNUMBER(D54),ISNUMBER(E54)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V51" s="21">
+      <c r="V51" s="22">
         <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50),D50&gt;E50),1,0)+IF(AND(ISNUMBER(D51),ISNUMBER(E51),E51&gt;D51),1,0)+IF(AND(ISNUMBER(D54),ISNUMBER(E54),E54&gt;D54),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W51" s="21">
+      <c r="W51" s="22">
         <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50),D50=E50),1,0)+IF(AND(ISNUMBER(D51),ISNUMBER(E51),D51=E51),1,0)+IF(AND(ISNUMBER(D54),ISNUMBER(E54),D54=E54),1,0)</f>
         <v>1</v>
       </c>
-      <c r="X51" s="21">
+      <c r="X51" s="22">
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
-      <c r="Y51" s="21">
+      <c r="Y51" s="22">
         <f>IF(ISNUMBER(D50),D50,0)+IF(ISNUMBER(E51),E51,0)+IF(ISNUMBER(E54),E54,0)</f>
         <v>2</v>
       </c>
-      <c r="Z51" s="21">
+      <c r="Z51" s="22">
         <f>IF(ISNUMBER(E50),E50,0)+IF(ISNUMBER(D51),D51,0)+IF(ISNUMBER(D54),D54,0)</f>
         <v>3</v>
       </c>
-      <c r="AA51" s="21">
+      <c r="AA51" s="22">
         <f t="shared" si="27"/>
         <v>-1</v>
       </c>
-      <c r="AB51" s="21">
+      <c r="AB51" s="22">
         <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AC51" s="21">
+      <c r="AC51" s="22">
         <f>AB51*1000000+(AA51+100)*1000+Y51*10+2</f>
         <v>4099022</v>
       </c>
@@ -5516,96 +5528,96 @@
       <c r="C52" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="17">
         <v>2.0</v>
       </c>
       <c r="E52" s="16">
-        <v>0.0</v>
-      </c>
-      <c r="F52" s="17" t="s">
+        <v>1.0</v>
+      </c>
+      <c r="F52" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G52" s="18" t="s">
+      <c r="G52" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I52" s="22">
+      <c r="I52" s="23">
         <v>4.0</v>
       </c>
-      <c r="J52" s="23" t="str">
+      <c r="J52" s="24" t="str">
         <f t="array" ref="J52">INDEX(T49:T52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
         <v>🇳🇿 Nueva Zelanda</v>
       </c>
-      <c r="K52" s="22">
+      <c r="K52" s="23">
         <f t="array" ref="K52">INDEX(U49:U52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
         <v>3</v>
       </c>
-      <c r="L52" s="22">
+      <c r="L52" s="23">
         <f t="array" ref="L52">INDEX(V49:V52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
         <v>0</v>
       </c>
-      <c r="M52" s="22">
+      <c r="M52" s="23">
         <f t="array" ref="M52">INDEX(W49:W52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
         <v>0</v>
       </c>
-      <c r="N52" s="22">
+      <c r="N52" s="23">
         <f t="array" ref="N52">INDEX(X49:X52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
         <v>3</v>
       </c>
-      <c r="O52" s="22">
+      <c r="O52" s="23">
         <f t="array" ref="O52">INDEX(Y49:Y52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
-        <v>0</v>
-      </c>
-      <c r="P52" s="22">
+        <v>1</v>
+      </c>
+      <c r="P52" s="23">
         <f t="array" ref="P52">INDEX(Z49:Z52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
         <v>6</v>
       </c>
-      <c r="Q52" s="22">
+      <c r="Q52" s="23">
         <f t="array" ref="Q52">INDEX(AA49:AA52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
-        <v>-6</v>
-      </c>
-      <c r="R52" s="22">
+        <v>-5</v>
+      </c>
+      <c r="R52" s="23">
         <f t="array" ref="R52">INDEX(AB49:AB52,MATCH(LARGE(AC49:AC52,4),AC49:AC52,0))</f>
         <v>0</v>
       </c>
-      <c r="T52" s="21" t="str">
+      <c r="T52" s="22" t="str">
         <f>F50</f>
         <v>🇳🇿 Nueva Zelanda</v>
       </c>
-      <c r="U52" s="21">
+      <c r="U52" s="22">
         <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50)),1,0)+IF(AND(ISNUMBER(D52),ISNUMBER(E52)),1,0)+IF(AND(ISNUMBER(D53),ISNUMBER(E53)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V52" s="21">
+      <c r="V52" s="22">
         <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50),E50&gt;D50),1,0)+IF(AND(ISNUMBER(D52),ISNUMBER(E52),E52&gt;D52),1,0)+IF(AND(ISNUMBER(D53),ISNUMBER(E53),E53&gt;D53),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W52" s="21">
+      <c r="W52" s="22">
         <f>IF(AND(ISNUMBER(D50),ISNUMBER(E50),D50=E50),1,0)+IF(AND(ISNUMBER(D52),ISNUMBER(E52),D52=E52),1,0)+IF(AND(ISNUMBER(D53),ISNUMBER(E53),D53=E53),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X52" s="21">
+      <c r="X52" s="22">
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="Y52" s="21">
+      <c r="Y52" s="22">
         <f>IF(ISNUMBER(E50),E50,0)+IF(ISNUMBER(E52),E52,0)+IF(ISNUMBER(E53),E53,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z52" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="22">
         <f>IF(ISNUMBER(D50),D50,0)+IF(ISNUMBER(D52),D52,0)+IF(ISNUMBER(D53),D53,0)</f>
         <v>6</v>
       </c>
-      <c r="AA52" s="21">
+      <c r="AA52" s="22">
         <f t="shared" si="27"/>
-        <v>-6</v>
-      </c>
-      <c r="AB52" s="21">
+        <v>-5</v>
+      </c>
+      <c r="AB52" s="22">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="AC52" s="21">
+      <c r="AC52" s="22">
         <f>AB52*1000000+(AA52+100)*1000+Y52*10+1</f>
-        <v>94001</v>
+        <v>95011</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
@@ -5615,16 +5627,16 @@
       <c r="C53" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="17">
         <v>3.0</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="17">
         <v>0.0</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="G53" s="18" t="s">
+      <c r="G53" s="19" t="s">
         <v>138</v>
       </c>
     </row>
@@ -5635,21 +5647,21 @@
       <c r="C54" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="17">
         <v>1.0</v>
       </c>
-      <c r="E54" s="16">
+      <c r="E54" s="17">
         <v>1.0</v>
       </c>
-      <c r="F54" s="17" t="s">
+      <c r="F54" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="G54" s="18" t="s">
+      <c r="G54" s="19" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="55" ht="18.0" customHeight="1">
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="25" t="s">
         <v>140</v>
       </c>
       <c r="C55" s="4"/>
@@ -5695,96 +5707,96 @@
       <c r="C56" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="17">
         <v>3.0</v>
       </c>
-      <c r="E56" s="16">
+      <c r="E56" s="17">
         <v>0.0</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="G56" s="18" t="s">
+      <c r="G56" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="I56" s="19">
+      <c r="I56" s="20">
         <v>1.0</v>
       </c>
-      <c r="J56" s="20" t="str">
+      <c r="J56" s="21" t="str">
         <f t="array" ref="J56">INDEX(T56:T59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
         <v>España 🇪🇸</v>
       </c>
-      <c r="K56" s="19">
+      <c r="K56" s="20">
         <f t="array" ref="K56">INDEX(U56:U59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
         <v>3</v>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="20">
         <f t="array" ref="L56">INDEX(V56:V59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
-        <v>2</v>
-      </c>
-      <c r="M56" s="19">
+        <v>3</v>
+      </c>
+      <c r="M56" s="20">
         <f t="array" ref="M56">INDEX(W56:W59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
-        <v>1</v>
-      </c>
-      <c r="N56" s="19">
+        <v>0</v>
+      </c>
+      <c r="N56" s="20">
         <f t="array" ref="N56">INDEX(X56:X59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
         <v>0</v>
       </c>
-      <c r="O56" s="19">
+      <c r="O56" s="20">
         <f t="array" ref="O56">INDEX(Y56:Y59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
-        <v>7</v>
-      </c>
-      <c r="P56" s="19">
+        <v>8</v>
+      </c>
+      <c r="P56" s="20">
         <f t="array" ref="P56">INDEX(Z56:Z59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
         <v>2</v>
       </c>
-      <c r="Q56" s="19">
+      <c r="Q56" s="20">
         <f t="array" ref="Q56">INDEX(AA56:AA59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
-        <v>5</v>
-      </c>
-      <c r="R56" s="19">
+        <v>6</v>
+      </c>
+      <c r="R56" s="20">
         <f t="array" ref="R56">INDEX(AB56:AB59,MATCH(LARGE(AC56:AC59,1),AC56:AC59,0))</f>
-        <v>7</v>
-      </c>
-      <c r="T56" s="21" t="str">
+        <v>9</v>
+      </c>
+      <c r="T56" s="22" t="str">
         <f>B56</f>
         <v>España 🇪🇸</v>
       </c>
-      <c r="U56" s="21">
+      <c r="U56" s="22">
         <f>IF(AND(ISNUMBER(D56),ISNUMBER(E56)),1,0)+IF(AND(ISNUMBER(D58),ISNUMBER(E58)),1,0)+IF(AND(ISNUMBER(D60),ISNUMBER(E60)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V56" s="21">
+      <c r="V56" s="22">
         <f>IF(AND(ISNUMBER(D56),ISNUMBER(E56),D56&gt;E56),1,0)+IF(AND(ISNUMBER(D58),ISNUMBER(E58),D58&gt;E58),1,0)+IF(AND(ISNUMBER(D60),ISNUMBER(E60),D60&gt;E60),1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="W56" s="21">
+        <v>3</v>
+      </c>
+      <c r="W56" s="22">
         <f>IF(AND(ISNUMBER(D56),ISNUMBER(E56),D56=E56),1,0)+IF(AND(ISNUMBER(D58),ISNUMBER(E58),D58=E58),1,0)+IF(AND(ISNUMBER(D60),ISNUMBER(E60),D60=E60),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="X56" s="21">
+        <v>0</v>
+      </c>
+      <c r="X56" s="22">
         <f t="shared" ref="X56:X59" si="30">U56-V56-W56</f>
         <v>0</v>
       </c>
-      <c r="Y56" s="21">
+      <c r="Y56" s="22">
         <f t="shared" ref="Y56:Z56" si="29">IF(ISNUMBER(D56),D56,0)+IF(ISNUMBER(D58),D58,0)+IF(ISNUMBER(D60),D60,0)</f>
-        <v>7</v>
-      </c>
-      <c r="Z56" s="21">
+        <v>8</v>
+      </c>
+      <c r="Z56" s="22">
         <f t="shared" si="29"/>
         <v>2</v>
       </c>
-      <c r="AA56" s="21">
+      <c r="AA56" s="22">
         <f t="shared" ref="AA56:AA59" si="31">Y56-Z56</f>
-        <v>5</v>
-      </c>
-      <c r="AB56" s="21">
+        <v>6</v>
+      </c>
+      <c r="AB56" s="22">
         <f t="shared" ref="AB56:AB59" si="32">V56*3+W56</f>
-        <v>7</v>
-      </c>
-      <c r="AC56" s="21">
+        <v>9</v>
+      </c>
+      <c r="AC56" s="22">
         <f>AB56*1000000+(AA56+100)*1000+Y56*10+4</f>
-        <v>7105074</v>
+        <v>9106084</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -5794,94 +5806,94 @@
       <c r="C57" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D57" s="16">
+      <c r="D57" s="17">
         <v>0.0</v>
       </c>
-      <c r="E57" s="16">
+      <c r="E57" s="17">
         <v>2.0</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G57" s="18" t="s">
+      <c r="G57" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="I57" s="19">
+      <c r="I57" s="20">
         <v>2.0</v>
       </c>
-      <c r="J57" s="20" t="str">
+      <c r="J57" s="21" t="str">
         <f t="array" ref="J57">INDEX(T56:T59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
         <v>🇺🇾 Uruguay</v>
       </c>
-      <c r="K57" s="19">
+      <c r="K57" s="20">
         <f t="array" ref="K57">INDEX(U56:U59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
         <v>3</v>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="20">
         <f t="array" ref="L57">INDEX(V56:V59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
         <v>2</v>
       </c>
-      <c r="M57" s="19">
+      <c r="M57" s="20">
         <f t="array" ref="M57">INDEX(W56:W59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="20">
+        <f t="array" ref="N57">INDEX(X56:X59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
         <v>1</v>
       </c>
-      <c r="N57" s="19">
-        <f t="array" ref="N57">INDEX(X56:X59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
-        <v>0</v>
-      </c>
-      <c r="O57" s="19">
+      <c r="O57" s="20">
         <f t="array" ref="O57">INDEX(Y56:Y59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
         <v>5</v>
       </c>
-      <c r="P57" s="19">
+      <c r="P57" s="20">
         <f t="array" ref="P57">INDEX(Z56:Z59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q57" s="19">
+        <v>2</v>
+      </c>
+      <c r="Q57" s="20">
         <f t="array" ref="Q57">INDEX(AA56:AA59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
-        <v>4</v>
-      </c>
-      <c r="R57" s="19">
+        <v>3</v>
+      </c>
+      <c r="R57" s="20">
         <f t="array" ref="R57">INDEX(AB56:AB59,MATCH(LARGE(AC56:AC59,2),AC56:AC59,0))</f>
-        <v>7</v>
-      </c>
-      <c r="T57" s="21" t="str">
+        <v>6</v>
+      </c>
+      <c r="T57" s="22" t="str">
         <f>F56</f>
         <v>🇨🇻 Cabo Verde</v>
       </c>
-      <c r="U57" s="21">
+      <c r="U57" s="22">
         <f>IF(AND(ISNUMBER(D59),ISNUMBER(E59)),1,0)+IF(AND(ISNUMBER(D61),ISNUMBER(E61)),1,0)+IF(AND(ISNUMBER(D56),ISNUMBER(E56)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V57" s="21">
+      <c r="V57" s="22">
         <f>IF(AND(ISNUMBER(D59),ISNUMBER(E59),D59&gt;E59),1,0)+IF(AND(ISNUMBER(D61),ISNUMBER(E61),D61&gt;E61),1,0)+IF(AND(ISNUMBER(D56),ISNUMBER(E56),E56&gt;D56),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W57" s="21">
+      <c r="W57" s="22">
         <f>IF(AND(ISNUMBER(D59),ISNUMBER(E59),D59=E59),1,0)+IF(AND(ISNUMBER(D61),ISNUMBER(E61),D61=E61),1,0)+IF(AND(ISNUMBER(D56),ISNUMBER(E56),D56=E56),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X57" s="21">
+      <c r="X57" s="22">
         <f t="shared" si="30"/>
         <v>3</v>
       </c>
-      <c r="Y57" s="21">
+      <c r="Y57" s="22">
         <f>IF(ISNUMBER(D59),D59,0)+IF(ISNUMBER(D61),D61,0)+IF(ISNUMBER(E56),E56,0)</f>
         <v>1</v>
       </c>
-      <c r="Z57" s="21">
+      <c r="Z57" s="22">
         <f>IF(ISNUMBER(E59),E59,0)+IF(ISNUMBER(E61),E61,0)+IF(ISNUMBER(D56),D56,0)</f>
         <v>7</v>
       </c>
-      <c r="AA57" s="21">
+      <c r="AA57" s="22">
         <f t="shared" si="31"/>
         <v>-6</v>
       </c>
-      <c r="AB57" s="21">
+      <c r="AB57" s="22">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="AC57" s="21">
+      <c r="AC57" s="22">
         <f>AB57*1000000+(AA57+100)*1000+Y57*10+3</f>
         <v>94013</v>
       </c>
@@ -5893,94 +5905,94 @@
       <c r="C58" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D58" s="16">
+      <c r="D58" s="17">
         <v>3.0</v>
       </c>
-      <c r="E58" s="16">
+      <c r="E58" s="17">
         <v>1.0</v>
       </c>
-      <c r="F58" s="17" t="s">
+      <c r="F58" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G58" s="18" t="s">
+      <c r="G58" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="I58" s="22">
+      <c r="I58" s="23">
         <v>3.0</v>
       </c>
-      <c r="J58" s="23" t="str">
+      <c r="J58" s="24" t="str">
         <f t="array" ref="J58">INDEX(T56:T59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>Arabia Saudí 🇸🇦</v>
       </c>
-      <c r="K58" s="22">
+      <c r="K58" s="23">
         <f t="array" ref="K58">INDEX(U56:U59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>3</v>
       </c>
-      <c r="L58" s="22">
+      <c r="L58" s="23">
         <f t="array" ref="L58">INDEX(V56:V59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>1</v>
       </c>
-      <c r="M58" s="22">
+      <c r="M58" s="23">
         <f t="array" ref="M58">INDEX(W56:W59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>0</v>
       </c>
-      <c r="N58" s="22">
+      <c r="N58" s="23">
         <f t="array" ref="N58">INDEX(X56:X59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>2</v>
       </c>
-      <c r="O58" s="22">
+      <c r="O58" s="23">
         <f t="array" ref="O58">INDEX(Y56:Y59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>3</v>
       </c>
-      <c r="P58" s="22">
+      <c r="P58" s="23">
         <f t="array" ref="P58">INDEX(Z56:Z59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>6</v>
       </c>
-      <c r="Q58" s="22">
+      <c r="Q58" s="23">
         <f t="array" ref="Q58">INDEX(AA56:AA59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>-3</v>
       </c>
-      <c r="R58" s="22">
+      <c r="R58" s="23">
         <f t="array" ref="R58">INDEX(AB56:AB59,MATCH(LARGE(AC56:AC59,3),AC56:AC59,0))</f>
         <v>3</v>
       </c>
-      <c r="T58" s="21" t="str">
+      <c r="T58" s="22" t="str">
         <f>B57</f>
         <v>Arabia Saudí 🇸🇦</v>
       </c>
-      <c r="U58" s="21">
+      <c r="U58" s="22">
         <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57)),1,0)+IF(AND(ISNUMBER(D58),ISNUMBER(E58)),1,0)+IF(AND(ISNUMBER(D61),ISNUMBER(E61)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V58" s="21">
+      <c r="V58" s="22">
         <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57),D57&gt;E57),1,0)+IF(AND(ISNUMBER(D58),ISNUMBER(E58),E58&gt;D58),1,0)+IF(AND(ISNUMBER(D61),ISNUMBER(E61),E61&gt;D61),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W58" s="21">
+      <c r="W58" s="22">
         <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57),D57=E57),1,0)+IF(AND(ISNUMBER(D58),ISNUMBER(E58),D58=E58),1,0)+IF(AND(ISNUMBER(D61),ISNUMBER(E61),D61=E61),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X58" s="21">
+      <c r="X58" s="22">
         <f t="shared" si="30"/>
         <v>2</v>
       </c>
-      <c r="Y58" s="21">
+      <c r="Y58" s="22">
         <f>IF(ISNUMBER(D57),D57,0)+IF(ISNUMBER(E58),E58,0)+IF(ISNUMBER(E61),E61,0)</f>
         <v>3</v>
       </c>
-      <c r="Z58" s="21">
+      <c r="Z58" s="22">
         <f>IF(ISNUMBER(E57),E57,0)+IF(ISNUMBER(D58),D58,0)+IF(ISNUMBER(D61),D61,0)</f>
         <v>6</v>
       </c>
-      <c r="AA58" s="21">
+      <c r="AA58" s="22">
         <f t="shared" si="31"/>
         <v>-3</v>
       </c>
-      <c r="AB58" s="21">
+      <c r="AB58" s="22">
         <f t="shared" si="32"/>
         <v>3</v>
       </c>
-      <c r="AC58" s="21">
+      <c r="AC58" s="22">
         <f>AB58*1000000+(AA58+100)*1000+Y58*10+2</f>
         <v>3097032</v>
       </c>
@@ -5992,96 +6004,96 @@
       <c r="C59" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="17">
         <v>0.0</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="17">
         <v>2.0</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="I59" s="22">
+      <c r="I59" s="23">
         <v>4.0</v>
       </c>
-      <c r="J59" s="23" t="str">
+      <c r="J59" s="24" t="str">
         <f t="array" ref="J59">INDEX(T56:T59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>🇨🇻 Cabo Verde</v>
       </c>
-      <c r="K59" s="22">
+      <c r="K59" s="23">
         <f t="array" ref="K59">INDEX(U56:U59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>3</v>
       </c>
-      <c r="L59" s="22">
+      <c r="L59" s="23">
         <f t="array" ref="L59">INDEX(V56:V59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>0</v>
       </c>
-      <c r="M59" s="22">
+      <c r="M59" s="23">
         <f t="array" ref="M59">INDEX(W56:W59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>0</v>
       </c>
-      <c r="N59" s="22">
+      <c r="N59" s="23">
         <f t="array" ref="N59">INDEX(X56:X59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>3</v>
       </c>
-      <c r="O59" s="22">
+      <c r="O59" s="23">
         <f t="array" ref="O59">INDEX(Y56:Y59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>1</v>
       </c>
-      <c r="P59" s="22">
+      <c r="P59" s="23">
         <f t="array" ref="P59">INDEX(Z56:Z59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>7</v>
       </c>
-      <c r="Q59" s="22">
+      <c r="Q59" s="23">
         <f t="array" ref="Q59">INDEX(AA56:AA59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>-6</v>
       </c>
-      <c r="R59" s="22">
+      <c r="R59" s="23">
         <f t="array" ref="R59">INDEX(AB56:AB59,MATCH(LARGE(AC56:AC59,4),AC56:AC59,0))</f>
         <v>0</v>
       </c>
-      <c r="T59" s="21" t="str">
+      <c r="T59" s="22" t="str">
         <f>F57</f>
         <v>🇺🇾 Uruguay</v>
       </c>
-      <c r="U59" s="21">
+      <c r="U59" s="22">
         <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57)),1,0)+IF(AND(ISNUMBER(D59),ISNUMBER(E59)),1,0)+IF(AND(ISNUMBER(D60),ISNUMBER(E60)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V59" s="21">
+      <c r="V59" s="22">
         <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57),E57&gt;D57),1,0)+IF(AND(ISNUMBER(D59),ISNUMBER(E59),E59&gt;D59),1,0)+IF(AND(ISNUMBER(D60),ISNUMBER(E60),E60&gt;D60),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W59" s="21">
+      <c r="W59" s="22">
         <f>IF(AND(ISNUMBER(D57),ISNUMBER(E57),D57=E57),1,0)+IF(AND(ISNUMBER(D59),ISNUMBER(E59),D59=E59),1,0)+IF(AND(ISNUMBER(D60),ISNUMBER(E60),D60=E60),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X59" s="22">
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
-      <c r="X59" s="21">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="Y59" s="21">
+      <c r="Y59" s="22">
         <f>IF(ISNUMBER(E57),E57,0)+IF(ISNUMBER(E59),E59,0)+IF(ISNUMBER(E60),E60,0)</f>
         <v>5</v>
       </c>
-      <c r="Z59" s="21">
+      <c r="Z59" s="22">
         <f>IF(ISNUMBER(D57),D57,0)+IF(ISNUMBER(D59),D59,0)+IF(ISNUMBER(D60),D60,0)</f>
-        <v>1</v>
-      </c>
-      <c r="AA59" s="21">
+        <v>2</v>
+      </c>
+      <c r="AA59" s="22">
         <f t="shared" si="31"/>
-        <v>4</v>
-      </c>
-      <c r="AB59" s="21">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="22">
         <f t="shared" si="32"/>
-        <v>7</v>
-      </c>
-      <c r="AC59" s="21">
+        <v>6</v>
+      </c>
+      <c r="AC59" s="22">
         <f>AB59*1000000+(AA59+100)*1000+Y59*10+1</f>
-        <v>7104051</v>
+        <v>6103051</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -6092,15 +6104,15 @@
         <v>153</v>
       </c>
       <c r="D60" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="E60" s="17">
         <v>1.0</v>
       </c>
-      <c r="E60" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="F60" s="17" t="s">
+      <c r="F60" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G60" s="18" t="s">
+      <c r="G60" s="19" t="s">
         <v>154</v>
       </c>
     </row>
@@ -6111,21 +6123,21 @@
       <c r="C61" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="17">
         <v>1.0</v>
       </c>
-      <c r="E61" s="16">
+      <c r="E61" s="17">
         <v>2.0</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F61" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G61" s="18" t="s">
+      <c r="G61" s="19" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="62" ht="18.0" customHeight="1">
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="25" t="s">
         <v>156</v>
       </c>
       <c r="C62" s="4"/>
@@ -6171,94 +6183,94 @@
       <c r="C63" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="17">
         <v>2.0</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="17">
         <v>0.0</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="G63" s="18" t="s">
+      <c r="G63" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="I63" s="19">
+      <c r="I63" s="20">
         <v>1.0</v>
       </c>
-      <c r="J63" s="20" t="str">
+      <c r="J63" s="21" t="str">
         <f t="array" ref="J63">INDEX(T63:T66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>Francia 🇫🇷</v>
       </c>
-      <c r="K63" s="19">
+      <c r="K63" s="20">
         <f t="array" ref="K63">INDEX(U63:U66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="20">
         <f t="array" ref="L63">INDEX(V63:V66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="M63" s="19">
+      <c r="M63" s="20">
         <f t="array" ref="M63">INDEX(W63:W66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="N63" s="19">
+      <c r="N63" s="20">
         <f t="array" ref="N63">INDEX(X63:X66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="O63" s="19">
+      <c r="O63" s="20">
         <f t="array" ref="O63">INDEX(Y63:Y66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>8</v>
       </c>
-      <c r="P63" s="19">
+      <c r="P63" s="20">
         <f t="array" ref="P63">INDEX(Z63:Z66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>1</v>
       </c>
-      <c r="Q63" s="19">
+      <c r="Q63" s="20">
         <f t="array" ref="Q63">INDEX(AA63:AA66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>7</v>
       </c>
-      <c r="R63" s="19">
+      <c r="R63" s="20">
         <f t="array" ref="R63">INDEX(AB63:AB66,MATCH(LARGE(AC63:AC66,1),AC63:AC66,0))</f>
         <v>9</v>
       </c>
-      <c r="T63" s="21" t="str">
+      <c r="T63" s="22" t="str">
         <f>B63</f>
         <v>Francia 🇫🇷</v>
       </c>
-      <c r="U63" s="21">
+      <c r="U63" s="22">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(E63)),1,0)+IF(AND(ISNUMBER(D65),ISNUMBER(E65)),1,0)+IF(AND(ISNUMBER(D67),ISNUMBER(E67)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V63" s="21">
+      <c r="V63" s="22">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(E63),D63&gt;E63),1,0)+IF(AND(ISNUMBER(D65),ISNUMBER(E65),D65&gt;E65),1,0)+IF(AND(ISNUMBER(D67),ISNUMBER(E67),D67&gt;E67),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W63" s="21">
+      <c r="W63" s="22">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(E63),D63=E63),1,0)+IF(AND(ISNUMBER(D65),ISNUMBER(E65),D65=E65),1,0)+IF(AND(ISNUMBER(D67),ISNUMBER(E67),D67=E67),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X63" s="21">
+      <c r="X63" s="22">
         <f t="shared" ref="X63:X66" si="34">U63-V63-W63</f>
         <v>0</v>
       </c>
-      <c r="Y63" s="21">
+      <c r="Y63" s="22">
         <f t="shared" ref="Y63:Z63" si="33">IF(ISNUMBER(D63),D63,0)+IF(ISNUMBER(D65),D65,0)+IF(ISNUMBER(D67),D67,0)</f>
         <v>8</v>
       </c>
-      <c r="Z63" s="21">
+      <c r="Z63" s="22">
         <f t="shared" si="33"/>
         <v>1</v>
       </c>
-      <c r="AA63" s="21">
+      <c r="AA63" s="22">
         <f t="shared" ref="AA63:AA66" si="35">Y63-Z63</f>
         <v>7</v>
       </c>
-      <c r="AB63" s="21">
+      <c r="AB63" s="22">
         <f t="shared" ref="AB63:AB66" si="36">V63*3+W63</f>
         <v>9</v>
       </c>
-      <c r="AC63" s="21">
+      <c r="AC63" s="22">
         <f>AB63*1000000+(AA63+100)*1000+Y63*10+4</f>
         <v>9107084</v>
       </c>
@@ -6270,94 +6282,94 @@
       <c r="C64" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="17">
         <v>3.0</v>
       </c>
-      <c r="E64" s="16">
+      <c r="E64" s="17">
         <v>0.0</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G64" s="18" t="s">
+      <c r="G64" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="I64" s="19">
+      <c r="I64" s="20">
         <v>2.0</v>
       </c>
-      <c r="J64" s="20" t="str">
+      <c r="J64" s="21" t="str">
         <f t="array" ref="J64">INDEX(T63:T66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>Noruega 🇳🇴</v>
       </c>
-      <c r="K64" s="19">
+      <c r="K64" s="20">
         <f t="array" ref="K64">INDEX(U63:U66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="20">
         <f t="array" ref="L64">INDEX(V63:V66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>2</v>
       </c>
-      <c r="M64" s="19">
+      <c r="M64" s="20">
         <f t="array" ref="M64">INDEX(W63:W66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="N64" s="19">
+      <c r="N64" s="20">
         <f t="array" ref="N64">INDEX(X63:X66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>1</v>
       </c>
-      <c r="O64" s="19">
+      <c r="O64" s="20">
         <f t="array" ref="O64">INDEX(Y63:Y66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>6</v>
       </c>
-      <c r="P64" s="19">
+      <c r="P64" s="20">
         <f t="array" ref="P64">INDEX(Z63:Z66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="Q64" s="19">
+      <c r="Q64" s="20">
         <f t="array" ref="Q64">INDEX(AA63:AA66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="R64" s="19">
+      <c r="R64" s="20">
         <f t="array" ref="R64">INDEX(AB63:AB66,MATCH(LARGE(AC63:AC66,2),AC63:AC66,0))</f>
         <v>6</v>
       </c>
-      <c r="T64" s="21" t="str">
+      <c r="T64" s="22" t="str">
         <f>F63</f>
         <v>🇸🇳 Senegal</v>
       </c>
-      <c r="U64" s="21">
+      <c r="U64" s="22">
         <f>IF(AND(ISNUMBER(D66),ISNUMBER(E66)),1,0)+IF(AND(ISNUMBER(D68),ISNUMBER(E68)),1,0)+IF(AND(ISNUMBER(D63),ISNUMBER(E63)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V64" s="21">
+      <c r="V64" s="22">
         <f>IF(AND(ISNUMBER(D66),ISNUMBER(E66),D66&gt;E66),1,0)+IF(AND(ISNUMBER(D68),ISNUMBER(E68),D68&gt;E68),1,0)+IF(AND(ISNUMBER(D63),ISNUMBER(E63),E63&gt;D63),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W64" s="21">
+      <c r="W64" s="22">
         <f>IF(AND(ISNUMBER(D66),ISNUMBER(E66),D66=E66),1,0)+IF(AND(ISNUMBER(D68),ISNUMBER(E68),D68=E68),1,0)+IF(AND(ISNUMBER(D63),ISNUMBER(E63),D63=E63),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X64" s="21">
+      <c r="X64" s="22">
         <f t="shared" si="34"/>
         <v>2</v>
       </c>
-      <c r="Y64" s="21">
+      <c r="Y64" s="22">
         <f>IF(ISNUMBER(D66),D66,0)+IF(ISNUMBER(D68),D68,0)+IF(ISNUMBER(E63),E63,0)</f>
         <v>3</v>
       </c>
-      <c r="Z64" s="21">
+      <c r="Z64" s="22">
         <f>IF(ISNUMBER(E66),E66,0)+IF(ISNUMBER(E68),E68,0)+IF(ISNUMBER(D63),D63,0)</f>
         <v>4</v>
       </c>
-      <c r="AA64" s="21">
+      <c r="AA64" s="22">
         <f t="shared" si="35"/>
         <v>-1</v>
       </c>
-      <c r="AB64" s="21">
+      <c r="AB64" s="22">
         <f t="shared" si="36"/>
         <v>3</v>
       </c>
-      <c r="AC64" s="21">
+      <c r="AC64" s="22">
         <f>AB64*1000000+(AA64+100)*1000+Y64*10+3</f>
         <v>3099033</v>
       </c>
@@ -6369,94 +6381,94 @@
       <c r="C65" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="17">
         <v>2.0</v>
       </c>
-      <c r="E65" s="16">
+      <c r="E65" s="17">
         <v>1.0</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="G65" s="18" t="s">
+      <c r="G65" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="I65" s="22">
+      <c r="I65" s="23">
         <v>3.0</v>
       </c>
-      <c r="J65" s="23" t="str">
+      <c r="J65" s="24" t="str">
         <f t="array" ref="J65">INDEX(T63:T66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>🇸🇳 Senegal</v>
       </c>
-      <c r="K65" s="22">
+      <c r="K65" s="23">
         <f t="array" ref="K65">INDEX(U63:U66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="L65" s="22">
+      <c r="L65" s="23">
         <f t="array" ref="L65">INDEX(V63:V66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>1</v>
       </c>
-      <c r="M65" s="22">
+      <c r="M65" s="23">
         <f t="array" ref="M65">INDEX(W63:W66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="N65" s="22">
+      <c r="N65" s="23">
         <f t="array" ref="N65">INDEX(X63:X66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>2</v>
       </c>
-      <c r="O65" s="22">
+      <c r="O65" s="23">
         <f t="array" ref="O65">INDEX(Y63:Y66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="P65" s="22">
+      <c r="P65" s="23">
         <f t="array" ref="P65">INDEX(Z63:Z66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>4</v>
       </c>
-      <c r="Q65" s="22">
+      <c r="Q65" s="23">
         <f t="array" ref="Q65">INDEX(AA63:AA66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>-1</v>
       </c>
-      <c r="R65" s="22">
+      <c r="R65" s="23">
         <f t="array" ref="R65">INDEX(AB63:AB66,MATCH(LARGE(AC63:AC66,3),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="T65" s="21" t="str">
+      <c r="T65" s="22" t="str">
         <f>B64</f>
         <v>Noruega 🇳🇴</v>
       </c>
-      <c r="U65" s="21">
+      <c r="U65" s="22">
         <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64)),1,0)+IF(AND(ISNUMBER(D65),ISNUMBER(E65)),1,0)+IF(AND(ISNUMBER(D68),ISNUMBER(E68)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V65" s="21">
+      <c r="V65" s="22">
         <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64),D64&gt;E64),1,0)+IF(AND(ISNUMBER(D65),ISNUMBER(E65),E65&gt;D65),1,0)+IF(AND(ISNUMBER(D68),ISNUMBER(E68),E68&gt;D68),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W65" s="21">
+      <c r="W65" s="22">
         <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64),D64=E64),1,0)+IF(AND(ISNUMBER(D65),ISNUMBER(E65),D65=E65),1,0)+IF(AND(ISNUMBER(D68),ISNUMBER(E68),D68=E68),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X65" s="21">
+      <c r="X65" s="22">
         <f t="shared" si="34"/>
         <v>1</v>
       </c>
-      <c r="Y65" s="21">
+      <c r="Y65" s="22">
         <f>IF(ISNUMBER(D64),D64,0)+IF(ISNUMBER(E65),E65,0)+IF(ISNUMBER(E68),E68,0)</f>
         <v>6</v>
       </c>
-      <c r="Z65" s="21">
+      <c r="Z65" s="22">
         <f>IF(ISNUMBER(E64),E64,0)+IF(ISNUMBER(D65),D65,0)+IF(ISNUMBER(D68),D68,0)</f>
         <v>3</v>
       </c>
-      <c r="AA65" s="21">
+      <c r="AA65" s="22">
         <f t="shared" si="35"/>
         <v>3</v>
       </c>
-      <c r="AB65" s="21">
+      <c r="AB65" s="22">
         <f t="shared" si="36"/>
         <v>6</v>
       </c>
-      <c r="AC65" s="21">
+      <c r="AC65" s="22">
         <f>AB65*1000000+(AA65+100)*1000+Y65*10+2</f>
         <v>6103062</v>
       </c>
@@ -6468,94 +6480,94 @@
       <c r="C66" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="17">
         <v>2.0</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="17">
         <v>0.0</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G66" s="18" t="s">
+      <c r="G66" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="I66" s="22">
+      <c r="I66" s="23">
         <v>4.0</v>
       </c>
-      <c r="J66" s="23" t="str">
+      <c r="J66" s="24" t="str">
         <f t="array" ref="J66">INDEX(T63:T66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>🇮🇶 Irak</v>
       </c>
-      <c r="K66" s="22">
+      <c r="K66" s="23">
         <f t="array" ref="K66">INDEX(U63:U66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="L66" s="22">
+      <c r="L66" s="23">
         <f t="array" ref="L66">INDEX(V63:V66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="M66" s="22">
+      <c r="M66" s="23">
         <f t="array" ref="M66">INDEX(W63:W66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="N66" s="22">
+      <c r="N66" s="23">
         <f t="array" ref="N66">INDEX(X63:X66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>3</v>
       </c>
-      <c r="O66" s="22">
+      <c r="O66" s="23">
         <f t="array" ref="O66">INDEX(Y63:Y66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="P66" s="22">
+      <c r="P66" s="23">
         <f t="array" ref="P66">INDEX(Z63:Z66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>9</v>
       </c>
-      <c r="Q66" s="22">
+      <c r="Q66" s="23">
         <f t="array" ref="Q66">INDEX(AA63:AA66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>-9</v>
       </c>
-      <c r="R66" s="22">
+      <c r="R66" s="23">
         <f t="array" ref="R66">INDEX(AB63:AB66,MATCH(LARGE(AC63:AC66,4),AC63:AC66,0))</f>
         <v>0</v>
       </c>
-      <c r="T66" s="21" t="str">
+      <c r="T66" s="22" t="str">
         <f>F64</f>
         <v>🇮🇶 Irak</v>
       </c>
-      <c r="U66" s="21">
+      <c r="U66" s="22">
         <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64)),1,0)+IF(AND(ISNUMBER(D66),ISNUMBER(E66)),1,0)+IF(AND(ISNUMBER(D67),ISNUMBER(E67)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V66" s="21">
+      <c r="V66" s="22">
         <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64),E64&gt;D64),1,0)+IF(AND(ISNUMBER(D66),ISNUMBER(E66),E66&gt;D66),1,0)+IF(AND(ISNUMBER(D67),ISNUMBER(E67),E67&gt;D67),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W66" s="21">
+      <c r="W66" s="22">
         <f>IF(AND(ISNUMBER(D64),ISNUMBER(E64),D64=E64),1,0)+IF(AND(ISNUMBER(D66),ISNUMBER(E66),D66=E66),1,0)+IF(AND(ISNUMBER(D67),ISNUMBER(E67),D67=E67),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X66" s="21">
+      <c r="X66" s="22">
         <f t="shared" si="34"/>
         <v>3</v>
       </c>
-      <c r="Y66" s="21">
+      <c r="Y66" s="22">
         <f>IF(ISNUMBER(E64),E64,0)+IF(ISNUMBER(E66),E66,0)+IF(ISNUMBER(E67),E67,0)</f>
         <v>0</v>
       </c>
-      <c r="Z66" s="21">
+      <c r="Z66" s="22">
         <f>IF(ISNUMBER(D64),D64,0)+IF(ISNUMBER(D66),D66,0)+IF(ISNUMBER(D67),D67,0)</f>
         <v>9</v>
       </c>
-      <c r="AA66" s="21">
+      <c r="AA66" s="22">
         <f t="shared" si="35"/>
         <v>-9</v>
       </c>
-      <c r="AB66" s="21">
+      <c r="AB66" s="22">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="AC66" s="21">
+      <c r="AC66" s="22">
         <f>AB66*1000000+(AA66+100)*1000+Y66*10+1</f>
         <v>91001</v>
       </c>
@@ -6567,16 +6579,16 @@
       <c r="C67" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D67" s="17">
         <v>4.0</v>
       </c>
-      <c r="E67" s="16">
+      <c r="E67" s="17">
         <v>0.0</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F67" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G67" s="18" t="s">
+      <c r="G67" s="19" t="s">
         <v>170</v>
       </c>
     </row>
@@ -6587,21 +6599,21 @@
       <c r="C68" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D68" s="17">
         <v>1.0</v>
       </c>
-      <c r="E68" s="16">
+      <c r="E68" s="17">
         <v>2.0</v>
       </c>
-      <c r="F68" s="17" t="s">
+      <c r="F68" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="G68" s="18" t="s">
+      <c r="G68" s="19" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="69" ht="18.0" customHeight="1">
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="25" t="s">
         <v>172</v>
       </c>
       <c r="C69" s="4"/>
@@ -6647,94 +6659,94 @@
       <c r="C70" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="D70" s="16">
+      <c r="D70" s="17">
         <v>2.0</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="17">
         <v>0.0</v>
       </c>
-      <c r="F70" s="17" t="s">
+      <c r="F70" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="18" t="s">
+      <c r="G70" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="I70" s="19">
+      <c r="I70" s="20">
         <v>1.0</v>
       </c>
-      <c r="J70" s="20" t="str">
+      <c r="J70" s="21" t="str">
         <f t="array" ref="J70">INDEX(T70:T73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>Argentina 🇦🇷</v>
       </c>
-      <c r="K70" s="19">
+      <c r="K70" s="20">
         <f t="array" ref="K70">INDEX(U70:U73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="L70" s="19">
+      <c r="L70" s="20">
         <f t="array" ref="L70">INDEX(V70:V73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="M70" s="19">
+      <c r="M70" s="20">
         <f t="array" ref="M70">INDEX(W70:W73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="N70" s="19">
+      <c r="N70" s="20">
         <f t="array" ref="N70">INDEX(X70:X73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="O70" s="19">
+      <c r="O70" s="20">
         <f t="array" ref="O70">INDEX(Y70:Y73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>8</v>
       </c>
-      <c r="P70" s="19">
+      <c r="P70" s="20">
         <f t="array" ref="P70">INDEX(Z70:Z73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>1</v>
       </c>
-      <c r="Q70" s="19">
+      <c r="Q70" s="20">
         <f t="array" ref="Q70">INDEX(AA70:AA73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>7</v>
       </c>
-      <c r="R70" s="19">
+      <c r="R70" s="20">
         <f t="array" ref="R70">INDEX(AB70:AB73,MATCH(LARGE(AC70:AC73,1),AC70:AC73,0))</f>
         <v>9</v>
       </c>
-      <c r="T70" s="21" t="str">
+      <c r="T70" s="22" t="str">
         <f>B70</f>
         <v>Argentina 🇦🇷</v>
       </c>
-      <c r="U70" s="21">
+      <c r="U70" s="22">
         <f>IF(AND(ISNUMBER(D70),ISNUMBER(E70)),1,0)+IF(AND(ISNUMBER(D72),ISNUMBER(E72)),1,0)+IF(AND(ISNUMBER(D74),ISNUMBER(E74)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V70" s="21">
+      <c r="V70" s="22">
         <f>IF(AND(ISNUMBER(D70),ISNUMBER(E70),D70&gt;E70),1,0)+IF(AND(ISNUMBER(D72),ISNUMBER(E72),D72&gt;E72),1,0)+IF(AND(ISNUMBER(D74),ISNUMBER(E74),D74&gt;E74),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W70" s="21">
+      <c r="W70" s="22">
         <f>IF(AND(ISNUMBER(D70),ISNUMBER(E70),D70=E70),1,0)+IF(AND(ISNUMBER(D72),ISNUMBER(E72),D72=E72),1,0)+IF(AND(ISNUMBER(D74),ISNUMBER(E74),D74=E74),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X70" s="21">
+      <c r="X70" s="22">
         <f t="shared" ref="X70:X73" si="38">U70-V70-W70</f>
         <v>0</v>
       </c>
-      <c r="Y70" s="21">
+      <c r="Y70" s="22">
         <f t="shared" ref="Y70:Z70" si="37">IF(ISNUMBER(D70),D70,0)+IF(ISNUMBER(D72),D72,0)+IF(ISNUMBER(D74),D74,0)</f>
         <v>8</v>
       </c>
-      <c r="Z70" s="21">
+      <c r="Z70" s="22">
         <f t="shared" si="37"/>
         <v>1</v>
       </c>
-      <c r="AA70" s="21">
+      <c r="AA70" s="22">
         <f t="shared" ref="AA70:AA73" si="39">Y70-Z70</f>
         <v>7</v>
       </c>
-      <c r="AB70" s="21">
+      <c r="AB70" s="22">
         <f t="shared" ref="AB70:AB73" si="40">V70*3+W70</f>
         <v>9</v>
       </c>
-      <c r="AC70" s="21">
+      <c r="AC70" s="22">
         <f>AB70*1000000+(AA70+100)*1000+Y70*10+4</f>
         <v>9107084</v>
       </c>
@@ -6746,94 +6758,94 @@
       <c r="C71" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D71" s="16">
+      <c r="D71" s="17">
         <v>2.0</v>
       </c>
-      <c r="E71" s="16">
+      <c r="E71" s="17">
         <v>0.0</v>
       </c>
-      <c r="F71" s="17" t="s">
+      <c r="F71" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="I71" s="19">
+      <c r="I71" s="20">
         <v>2.0</v>
       </c>
-      <c r="J71" s="20" t="str">
+      <c r="J71" s="21" t="str">
         <f t="array" ref="J71">INDEX(T70:T73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>Austria 🇦🇹</v>
       </c>
-      <c r="K71" s="19">
+      <c r="K71" s="20">
         <f t="array" ref="K71">INDEX(U70:U73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="L71" s="19">
+      <c r="L71" s="20">
         <f t="array" ref="L71">INDEX(V70:V73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>2</v>
       </c>
-      <c r="M71" s="19">
+      <c r="M71" s="20">
         <f t="array" ref="M71">INDEX(W70:W73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="N71" s="19">
+      <c r="N71" s="20">
         <f t="array" ref="N71">INDEX(X70:X73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>1</v>
       </c>
-      <c r="O71" s="19">
+      <c r="O71" s="20">
         <f t="array" ref="O71">INDEX(Y70:Y73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>5</v>
       </c>
-      <c r="P71" s="19">
+      <c r="P71" s="20">
         <f t="array" ref="P71">INDEX(Z70:Z73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>2</v>
       </c>
-      <c r="Q71" s="19">
+      <c r="Q71" s="20">
         <f t="array" ref="Q71">INDEX(AA70:AA73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="R71" s="19">
+      <c r="R71" s="20">
         <f t="array" ref="R71">INDEX(AB70:AB73,MATCH(LARGE(AC70:AC73,2),AC70:AC73,0))</f>
         <v>6</v>
       </c>
-      <c r="T71" s="21" t="str">
+      <c r="T71" s="22" t="str">
         <f>F70</f>
         <v>🇩🇿 Argelia</v>
       </c>
-      <c r="U71" s="21">
+      <c r="U71" s="22">
         <f>IF(AND(ISNUMBER(D73),ISNUMBER(E73)),1,0)+IF(AND(ISNUMBER(D75),ISNUMBER(E75)),1,0)+IF(AND(ISNUMBER(D70),ISNUMBER(E70)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V71" s="21">
+      <c r="V71" s="22">
         <f>IF(AND(ISNUMBER(D73),ISNUMBER(E73),D73&gt;E73),1,0)+IF(AND(ISNUMBER(D75),ISNUMBER(E75),D75&gt;E75),1,0)+IF(AND(ISNUMBER(D70),ISNUMBER(E70),E70&gt;D70),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W71" s="21">
+      <c r="W71" s="22">
         <f>IF(AND(ISNUMBER(D73),ISNUMBER(E73),D73=E73),1,0)+IF(AND(ISNUMBER(D75),ISNUMBER(E75),D75=E75),1,0)+IF(AND(ISNUMBER(D70),ISNUMBER(E70),D70=E70),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X71" s="21">
+      <c r="X71" s="22">
         <f t="shared" si="38"/>
         <v>2</v>
       </c>
-      <c r="Y71" s="21">
+      <c r="Y71" s="22">
         <f>IF(ISNUMBER(D73),D73,0)+IF(ISNUMBER(D75),D75,0)+IF(ISNUMBER(E70),E70,0)</f>
         <v>2</v>
       </c>
-      <c r="Z71" s="21">
+      <c r="Z71" s="22">
         <f>IF(ISNUMBER(E73),E73,0)+IF(ISNUMBER(E75),E75,0)+IF(ISNUMBER(D70),D70,0)</f>
         <v>4</v>
       </c>
-      <c r="AA71" s="21">
+      <c r="AA71" s="22">
         <f t="shared" si="39"/>
         <v>-2</v>
       </c>
-      <c r="AB71" s="21">
+      <c r="AB71" s="22">
         <f t="shared" si="40"/>
         <v>3</v>
       </c>
-      <c r="AC71" s="21">
+      <c r="AC71" s="22">
         <f>AB71*1000000+(AA71+100)*1000+Y71*10+3</f>
         <v>3098023</v>
       </c>
@@ -6845,94 +6857,94 @@
       <c r="C72" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="17">
         <v>2.0</v>
       </c>
-      <c r="E72" s="16">
+      <c r="E72" s="17">
         <v>1.0</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="18" t="s">
+      <c r="G72" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="I72" s="22">
+      <c r="I72" s="23">
         <v>3.0</v>
       </c>
-      <c r="J72" s="23" t="str">
+      <c r="J72" s="24" t="str">
         <f t="array" ref="J72">INDEX(T70:T73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>🇩🇿 Argelia</v>
       </c>
-      <c r="K72" s="22">
+      <c r="K72" s="23">
         <f t="array" ref="K72">INDEX(U70:U73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="L72" s="22">
+      <c r="L72" s="23">
         <f t="array" ref="L72">INDEX(V70:V73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>1</v>
       </c>
-      <c r="M72" s="22">
+      <c r="M72" s="23">
         <f t="array" ref="M72">INDEX(W70:W73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="N72" s="22">
+      <c r="N72" s="23">
         <f t="array" ref="N72">INDEX(X70:X73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>2</v>
       </c>
-      <c r="O72" s="22">
+      <c r="O72" s="23">
         <f t="array" ref="O72">INDEX(Y70:Y73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>2</v>
       </c>
-      <c r="P72" s="22">
+      <c r="P72" s="23">
         <f t="array" ref="P72">INDEX(Z70:Z73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>4</v>
       </c>
-      <c r="Q72" s="22">
+      <c r="Q72" s="23">
         <f t="array" ref="Q72">INDEX(AA70:AA73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>-2</v>
       </c>
-      <c r="R72" s="22">
+      <c r="R72" s="23">
         <f t="array" ref="R72">INDEX(AB70:AB73,MATCH(LARGE(AC70:AC73,3),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="T72" s="21" t="str">
+      <c r="T72" s="22" t="str">
         <f>B71</f>
         <v>Austria 🇦🇹</v>
       </c>
-      <c r="U72" s="21">
+      <c r="U72" s="22">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(E71)),1,0)+IF(AND(ISNUMBER(D72),ISNUMBER(E72)),1,0)+IF(AND(ISNUMBER(D75),ISNUMBER(E75)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V72" s="21">
+      <c r="V72" s="22">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(E71),D71&gt;E71),1,0)+IF(AND(ISNUMBER(D72),ISNUMBER(E72),E72&gt;D72),1,0)+IF(AND(ISNUMBER(D75),ISNUMBER(E75),E75&gt;D75),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W72" s="21">
+      <c r="W72" s="22">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(E71),D71=E71),1,0)+IF(AND(ISNUMBER(D72),ISNUMBER(E72),D72=E72),1,0)+IF(AND(ISNUMBER(D75),ISNUMBER(E75),D75=E75),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X72" s="21">
+      <c r="X72" s="22">
         <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="Y72" s="21">
+      <c r="Y72" s="22">
         <f>IF(ISNUMBER(D71),D71,0)+IF(ISNUMBER(E72),E72,0)+IF(ISNUMBER(E75),E75,0)</f>
         <v>5</v>
       </c>
-      <c r="Z72" s="21">
+      <c r="Z72" s="22">
         <f>IF(ISNUMBER(E71),E71,0)+IF(ISNUMBER(D72),D72,0)+IF(ISNUMBER(D75),D75,0)</f>
         <v>2</v>
       </c>
-      <c r="AA72" s="21">
+      <c r="AA72" s="22">
         <f t="shared" si="39"/>
         <v>3</v>
       </c>
-      <c r="AB72" s="21">
+      <c r="AB72" s="22">
         <f t="shared" si="40"/>
         <v>6</v>
       </c>
-      <c r="AC72" s="21">
+      <c r="AC72" s="22">
         <f>AB72*1000000+(AA72+100)*1000+Y72*10+2</f>
         <v>6103052</v>
       </c>
@@ -6944,94 +6956,94 @@
       <c r="C73" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="17">
         <v>2.0</v>
       </c>
-      <c r="E73" s="16">
+      <c r="E73" s="17">
         <v>0.0</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="F73" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="G73" s="18" t="s">
+      <c r="G73" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="I73" s="22">
+      <c r="I73" s="23">
         <v>4.0</v>
       </c>
-      <c r="J73" s="23" t="str">
+      <c r="J73" s="24" t="str">
         <f t="array" ref="J73">INDEX(T70:T73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>🇯🇴 Jordania</v>
       </c>
-      <c r="K73" s="22">
+      <c r="K73" s="23">
         <f t="array" ref="K73">INDEX(U70:U73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="L73" s="22">
+      <c r="L73" s="23">
         <f t="array" ref="L73">INDEX(V70:V73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="M73" s="22">
+      <c r="M73" s="23">
         <f t="array" ref="M73">INDEX(W70:W73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="N73" s="22">
+      <c r="N73" s="23">
         <f t="array" ref="N73">INDEX(X70:X73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>3</v>
       </c>
-      <c r="O73" s="22">
+      <c r="O73" s="23">
         <f t="array" ref="O73">INDEX(Y70:Y73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="P73" s="22">
+      <c r="P73" s="23">
         <f t="array" ref="P73">INDEX(Z70:Z73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>8</v>
       </c>
-      <c r="Q73" s="22">
+      <c r="Q73" s="23">
         <f t="array" ref="Q73">INDEX(AA70:AA73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>-8</v>
       </c>
-      <c r="R73" s="22">
+      <c r="R73" s="23">
         <f t="array" ref="R73">INDEX(AB70:AB73,MATCH(LARGE(AC70:AC73,4),AC70:AC73,0))</f>
         <v>0</v>
       </c>
-      <c r="T73" s="21" t="str">
+      <c r="T73" s="22" t="str">
         <f>F71</f>
         <v>🇯🇴 Jordania</v>
       </c>
-      <c r="U73" s="21">
+      <c r="U73" s="22">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(E71)),1,0)+IF(AND(ISNUMBER(D73),ISNUMBER(E73)),1,0)+IF(AND(ISNUMBER(D74),ISNUMBER(E74)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V73" s="21">
+      <c r="V73" s="22">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(E71),E71&gt;D71),1,0)+IF(AND(ISNUMBER(D73),ISNUMBER(E73),E73&gt;D73),1,0)+IF(AND(ISNUMBER(D74),ISNUMBER(E74),E74&gt;D74),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W73" s="21">
+      <c r="W73" s="22">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(E71),D71=E71),1,0)+IF(AND(ISNUMBER(D73),ISNUMBER(E73),D73=E73),1,0)+IF(AND(ISNUMBER(D74),ISNUMBER(E74),D74=E74),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X73" s="21">
+      <c r="X73" s="22">
         <f t="shared" si="38"/>
         <v>3</v>
       </c>
-      <c r="Y73" s="21">
+      <c r="Y73" s="22">
         <f>IF(ISNUMBER(E71),E71,0)+IF(ISNUMBER(E73),E73,0)+IF(ISNUMBER(E74),E74,0)</f>
         <v>0</v>
       </c>
-      <c r="Z73" s="21">
+      <c r="Z73" s="22">
         <f>IF(ISNUMBER(D71),D71,0)+IF(ISNUMBER(D73),D73,0)+IF(ISNUMBER(D74),D74,0)</f>
         <v>8</v>
       </c>
-      <c r="AA73" s="21">
+      <c r="AA73" s="22">
         <f t="shared" si="39"/>
         <v>-8</v>
       </c>
-      <c r="AB73" s="21">
+      <c r="AB73" s="22">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="AC73" s="21">
+      <c r="AC73" s="22">
         <f>AB73*1000000+(AA73+100)*1000+Y73*10+1</f>
         <v>92001</v>
       </c>
@@ -7043,16 +7055,16 @@
       <c r="C74" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="17">
         <v>4.0</v>
       </c>
-      <c r="E74" s="16">
+      <c r="E74" s="17">
         <v>0.0</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F74" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="G74" s="19" t="s">
         <v>186</v>
       </c>
     </row>
@@ -7063,21 +7075,21 @@
       <c r="C75" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="17">
         <v>0.0</v>
       </c>
-      <c r="E75" s="16">
+      <c r="E75" s="17">
         <v>2.0</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="G75" s="18" t="s">
+      <c r="G75" s="19" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="76" ht="18.0" customHeight="1">
-      <c r="B76" s="24" t="s">
+      <c r="B76" s="25" t="s">
         <v>188</v>
       </c>
       <c r="C76" s="4"/>
@@ -7123,94 +7135,94 @@
       <c r="C77" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="D77" s="16">
+      <c r="D77" s="17">
         <v>2.0</v>
       </c>
-      <c r="E77" s="16">
+      <c r="E77" s="17">
         <v>1.0</v>
       </c>
-      <c r="F77" s="17" t="s">
+      <c r="F77" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="G77" s="18" t="s">
+      <c r="G77" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I77" s="19">
+      <c r="I77" s="20">
         <v>1.0</v>
       </c>
-      <c r="J77" s="20" t="str">
+      <c r="J77" s="21" t="str">
         <f t="array" ref="J77">INDEX(T77:T80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>Portugal 🇵🇹</v>
       </c>
-      <c r="K77" s="19">
+      <c r="K77" s="20">
         <f t="array" ref="K77">INDEX(U77:U80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>3</v>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="20">
         <f t="array" ref="L77">INDEX(V77:V80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>3</v>
       </c>
-      <c r="M77" s="19">
+      <c r="M77" s="20">
         <f t="array" ref="M77">INDEX(W77:W80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>0</v>
       </c>
-      <c r="N77" s="19">
+      <c r="N77" s="20">
         <f t="array" ref="N77">INDEX(X77:X80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>0</v>
       </c>
-      <c r="O77" s="19">
+      <c r="O77" s="20">
         <f t="array" ref="O77">INDEX(Y77:Y80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>8</v>
       </c>
-      <c r="P77" s="19">
+      <c r="P77" s="20">
         <f t="array" ref="P77">INDEX(Z77:Z80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="Q77" s="19">
+      <c r="Q77" s="20">
         <f t="array" ref="Q77">INDEX(AA77:AA80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>7</v>
       </c>
-      <c r="R77" s="19">
+      <c r="R77" s="20">
         <f t="array" ref="R77">INDEX(AB77:AB80,MATCH(LARGE(AC77:AC80,1),AC77:AC80,0))</f>
         <v>9</v>
       </c>
-      <c r="T77" s="21" t="str">
+      <c r="T77" s="22" t="str">
         <f>B77</f>
         <v>Portugal 🇵🇹</v>
       </c>
-      <c r="U77" s="21">
+      <c r="U77" s="22">
         <f>IF(AND(ISNUMBER(D77),ISNUMBER(E77)),1,0)+IF(AND(ISNUMBER(D79),ISNUMBER(E79)),1,0)+IF(AND(ISNUMBER(D81),ISNUMBER(E81)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V77" s="21">
+      <c r="V77" s="22">
         <f>IF(AND(ISNUMBER(D77),ISNUMBER(E77),D77&gt;E77),1,0)+IF(AND(ISNUMBER(D79),ISNUMBER(E79),D79&gt;E79),1,0)+IF(AND(ISNUMBER(D81),ISNUMBER(E81),D81&gt;E81),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W77" s="21">
+      <c r="W77" s="22">
         <f>IF(AND(ISNUMBER(D77),ISNUMBER(E77),D77=E77),1,0)+IF(AND(ISNUMBER(D79),ISNUMBER(E79),D79=E79),1,0)+IF(AND(ISNUMBER(D81),ISNUMBER(E81),D81=E81),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X77" s="21">
+      <c r="X77" s="22">
         <f t="shared" ref="X77:X80" si="42">U77-V77-W77</f>
         <v>0</v>
       </c>
-      <c r="Y77" s="21">
+      <c r="Y77" s="22">
         <f t="shared" ref="Y77:Z77" si="41">IF(ISNUMBER(D77),D77,0)+IF(ISNUMBER(D79),D79,0)+IF(ISNUMBER(D81),D81,0)</f>
         <v>8</v>
       </c>
-      <c r="Z77" s="21">
+      <c r="Z77" s="22">
         <f t="shared" si="41"/>
         <v>1</v>
       </c>
-      <c r="AA77" s="21">
+      <c r="AA77" s="22">
         <f t="shared" ref="AA77:AA80" si="43">Y77-Z77</f>
         <v>7</v>
       </c>
-      <c r="AB77" s="21">
+      <c r="AB77" s="22">
         <f t="shared" ref="AB77:AB80" si="44">V77*3+W77</f>
         <v>9</v>
       </c>
-      <c r="AC77" s="21">
+      <c r="AC77" s="22">
         <f>AB77*1000000+(AA77+100)*1000+Y77*10+4</f>
         <v>9107084</v>
       </c>
@@ -7222,94 +7234,94 @@
       <c r="C78" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D78" s="16">
+      <c r="D78" s="17">
         <v>1.0</v>
       </c>
-      <c r="E78" s="16">
+      <c r="E78" s="17">
         <v>1.0</v>
       </c>
-      <c r="F78" s="17" t="s">
+      <c r="F78" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="G78" s="18" t="s">
+      <c r="G78" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="I78" s="19">
+      <c r="I78" s="20">
         <v>2.0</v>
       </c>
-      <c r="J78" s="20" t="str">
+      <c r="J78" s="21" t="str">
         <f t="array" ref="J78">INDEX(T77:T80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>🇨🇴 Colombia</v>
       </c>
-      <c r="K78" s="19">
+      <c r="K78" s="20">
         <f t="array" ref="K78">INDEX(U77:U80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>3</v>
       </c>
-      <c r="L78" s="19">
+      <c r="L78" s="20">
         <f t="array" ref="L78">INDEX(V77:V80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>2</v>
       </c>
-      <c r="M78" s="19">
+      <c r="M78" s="20">
         <f t="array" ref="M78">INDEX(W77:W80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>0</v>
       </c>
-      <c r="N78" s="19">
+      <c r="N78" s="20">
         <f t="array" ref="N78">INDEX(X77:X80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="O78" s="19">
+      <c r="O78" s="20">
         <f t="array" ref="O78">INDEX(Y77:Y80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>5</v>
       </c>
-      <c r="P78" s="19">
+      <c r="P78" s="20">
         <f t="array" ref="P78">INDEX(Z77:Z80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>2</v>
       </c>
-      <c r="Q78" s="19">
+      <c r="Q78" s="20">
         <f t="array" ref="Q78">INDEX(AA77:AA80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>3</v>
       </c>
-      <c r="R78" s="19">
+      <c r="R78" s="20">
         <f t="array" ref="R78">INDEX(AB77:AB80,MATCH(LARGE(AC77:AC80,2),AC77:AC80,0))</f>
         <v>6</v>
       </c>
-      <c r="T78" s="21" t="str">
+      <c r="T78" s="22" t="str">
         <f>F77</f>
         <v>🇨🇴 Colombia</v>
       </c>
-      <c r="U78" s="21">
+      <c r="U78" s="22">
         <f>IF(AND(ISNUMBER(D80),ISNUMBER(E80)),1,0)+IF(AND(ISNUMBER(D82),ISNUMBER(E82)),1,0)+IF(AND(ISNUMBER(D77),ISNUMBER(E77)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V78" s="21">
+      <c r="V78" s="22">
         <f>IF(AND(ISNUMBER(D80),ISNUMBER(E80),D80&gt;E80),1,0)+IF(AND(ISNUMBER(D82),ISNUMBER(E82),D82&gt;E82),1,0)+IF(AND(ISNUMBER(D77),ISNUMBER(E77),E77&gt;D77),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W78" s="21">
+      <c r="W78" s="22">
         <f>IF(AND(ISNUMBER(D80),ISNUMBER(E80),D80=E80),1,0)+IF(AND(ISNUMBER(D82),ISNUMBER(E82),D82=E82),1,0)+IF(AND(ISNUMBER(D77),ISNUMBER(E77),D77=E77),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X78" s="21">
+      <c r="X78" s="22">
         <f t="shared" si="42"/>
         <v>1</v>
       </c>
-      <c r="Y78" s="21">
+      <c r="Y78" s="22">
         <f>IF(ISNUMBER(D80),D80,0)+IF(ISNUMBER(D82),D82,0)+IF(ISNUMBER(E77),E77,0)</f>
         <v>5</v>
       </c>
-      <c r="Z78" s="21">
+      <c r="Z78" s="22">
         <f>IF(ISNUMBER(E80),E80,0)+IF(ISNUMBER(E82),E82,0)+IF(ISNUMBER(D77),D77,0)</f>
         <v>2</v>
       </c>
-      <c r="AA78" s="21">
+      <c r="AA78" s="22">
         <f t="shared" si="43"/>
         <v>3</v>
       </c>
-      <c r="AB78" s="21">
+      <c r="AB78" s="22">
         <f t="shared" si="44"/>
         <v>6</v>
       </c>
-      <c r="AC78" s="21">
+      <c r="AC78" s="22">
         <f>AB78*1000000+(AA78+100)*1000+Y78*10+3</f>
         <v>6103053</v>
       </c>
@@ -7321,94 +7333,94 @@
       <c r="C79" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="17">
         <v>3.0</v>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="17">
         <v>0.0</v>
       </c>
-      <c r="F79" s="17" t="s">
+      <c r="F79" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="G79" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="I79" s="22">
+      <c r="I79" s="23">
         <v>3.0</v>
       </c>
-      <c r="J79" s="23" t="str">
+      <c r="J79" s="24" t="str">
         <f t="array" ref="J79">INDEX(T77:T80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>Uzbekistán 🇺🇿</v>
       </c>
-      <c r="K79" s="22">
+      <c r="K79" s="23">
         <f t="array" ref="K79">INDEX(U77:U80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>3</v>
       </c>
-      <c r="L79" s="22">
+      <c r="L79" s="23">
         <f t="array" ref="L79">INDEX(V77:V80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>0</v>
       </c>
-      <c r="M79" s="22">
+      <c r="M79" s="23">
         <f t="array" ref="M79">INDEX(W77:W80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="N79" s="22">
+      <c r="N79" s="23">
         <f t="array" ref="N79">INDEX(X77:X80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>2</v>
       </c>
-      <c r="O79" s="22">
+      <c r="O79" s="23">
         <f t="array" ref="O79">INDEX(Y77:Y80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="P79" s="22">
+      <c r="P79" s="23">
         <f t="array" ref="P79">INDEX(Z77:Z80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>6</v>
       </c>
-      <c r="Q79" s="22">
+      <c r="Q79" s="23">
         <f t="array" ref="Q79">INDEX(AA77:AA80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>-5</v>
       </c>
-      <c r="R79" s="22">
+      <c r="R79" s="23">
         <f t="array" ref="R79">INDEX(AB77:AB80,MATCH(LARGE(AC77:AC80,3),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="T79" s="21" t="str">
+      <c r="T79" s="22" t="str">
         <f>B78</f>
         <v>Uzbekistán 🇺🇿</v>
       </c>
-      <c r="U79" s="21">
+      <c r="U79" s="22">
         <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78)),1,0)+IF(AND(ISNUMBER(D79),ISNUMBER(E79)),1,0)+IF(AND(ISNUMBER(D82),ISNUMBER(E82)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V79" s="21">
+      <c r="V79" s="22">
         <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78),D78&gt;E78),1,0)+IF(AND(ISNUMBER(D79),ISNUMBER(E79),E79&gt;D79),1,0)+IF(AND(ISNUMBER(D82),ISNUMBER(E82),E82&gt;D82),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W79" s="21">
+      <c r="W79" s="22">
         <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78),D78=E78),1,0)+IF(AND(ISNUMBER(D79),ISNUMBER(E79),D79=E79),1,0)+IF(AND(ISNUMBER(D82),ISNUMBER(E82),D82=E82),1,0)</f>
         <v>1</v>
       </c>
-      <c r="X79" s="21">
+      <c r="X79" s="22">
         <f t="shared" si="42"/>
         <v>2</v>
       </c>
-      <c r="Y79" s="21">
+      <c r="Y79" s="22">
         <f>IF(ISNUMBER(D78),D78,0)+IF(ISNUMBER(E79),E79,0)+IF(ISNUMBER(E82),E82,0)</f>
         <v>1</v>
       </c>
-      <c r="Z79" s="21">
+      <c r="Z79" s="22">
         <f>IF(ISNUMBER(E78),E78,0)+IF(ISNUMBER(D79),D79,0)+IF(ISNUMBER(D82),D82,0)</f>
         <v>6</v>
       </c>
-      <c r="AA79" s="21">
+      <c r="AA79" s="22">
         <f t="shared" si="43"/>
         <v>-5</v>
       </c>
-      <c r="AB79" s="21">
+      <c r="AB79" s="22">
         <f t="shared" si="44"/>
         <v>1</v>
       </c>
-      <c r="AC79" s="21">
+      <c r="AC79" s="22">
         <f>AB79*1000000+(AA79+100)*1000+Y79*10+2</f>
         <v>1095012</v>
       </c>
@@ -7420,94 +7432,94 @@
       <c r="C80" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="D80" s="16">
+      <c r="D80" s="17">
         <v>2.0</v>
       </c>
-      <c r="E80" s="16">
+      <c r="E80" s="17">
         <v>0.0</v>
       </c>
-      <c r="F80" s="17" t="s">
+      <c r="F80" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="G80" s="18" t="s">
+      <c r="G80" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="I80" s="22">
+      <c r="I80" s="23">
         <v>4.0</v>
       </c>
-      <c r="J80" s="23" t="str">
+      <c r="J80" s="24" t="str">
         <f t="array" ref="J80">INDEX(T77:T80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>🇨🇩 RD Congo</v>
       </c>
-      <c r="K80" s="22">
+      <c r="K80" s="23">
         <f t="array" ref="K80">INDEX(U77:U80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>3</v>
       </c>
-      <c r="L80" s="22">
+      <c r="L80" s="23">
         <f t="array" ref="L80">INDEX(V77:V80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>0</v>
       </c>
-      <c r="M80" s="22">
+      <c r="M80" s="23">
         <f t="array" ref="M80">INDEX(W77:W80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="N80" s="22">
+      <c r="N80" s="23">
         <f t="array" ref="N80">INDEX(X77:X80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>2</v>
       </c>
-      <c r="O80" s="22">
+      <c r="O80" s="23">
         <f t="array" ref="O80">INDEX(Y77:Y80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="P80" s="22">
+      <c r="P80" s="23">
         <f t="array" ref="P80">INDEX(Z77:Z80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>6</v>
       </c>
-      <c r="Q80" s="22">
+      <c r="Q80" s="23">
         <f t="array" ref="Q80">INDEX(AA77:AA80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>-5</v>
       </c>
-      <c r="R80" s="22">
+      <c r="R80" s="23">
         <f t="array" ref="R80">INDEX(AB77:AB80,MATCH(LARGE(AC77:AC80,4),AC77:AC80,0))</f>
         <v>1</v>
       </c>
-      <c r="T80" s="21" t="str">
+      <c r="T80" s="22" t="str">
         <f>F78</f>
         <v>🇨🇩 RD Congo</v>
       </c>
-      <c r="U80" s="21">
+      <c r="U80" s="22">
         <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78)),1,0)+IF(AND(ISNUMBER(D80),ISNUMBER(E80)),1,0)+IF(AND(ISNUMBER(D81),ISNUMBER(E81)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V80" s="21">
+      <c r="V80" s="22">
         <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78),E78&gt;D78),1,0)+IF(AND(ISNUMBER(D80),ISNUMBER(E80),E80&gt;D80),1,0)+IF(AND(ISNUMBER(D81),ISNUMBER(E81),E81&gt;D81),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W80" s="21">
+      <c r="W80" s="22">
         <f>IF(AND(ISNUMBER(D78),ISNUMBER(E78),D78=E78),1,0)+IF(AND(ISNUMBER(D80),ISNUMBER(E80),D80=E80),1,0)+IF(AND(ISNUMBER(D81),ISNUMBER(E81),D81=E81),1,0)</f>
         <v>1</v>
       </c>
-      <c r="X80" s="21">
+      <c r="X80" s="22">
         <f t="shared" si="42"/>
         <v>2</v>
       </c>
-      <c r="Y80" s="21">
+      <c r="Y80" s="22">
         <f>IF(ISNUMBER(E78),E78,0)+IF(ISNUMBER(E80),E80,0)+IF(ISNUMBER(E81),E81,0)</f>
         <v>1</v>
       </c>
-      <c r="Z80" s="21">
+      <c r="Z80" s="22">
         <f>IF(ISNUMBER(D78),D78,0)+IF(ISNUMBER(D80),D80,0)+IF(ISNUMBER(D81),D81,0)</f>
         <v>6</v>
       </c>
-      <c r="AA80" s="21">
+      <c r="AA80" s="22">
         <f t="shared" si="43"/>
         <v>-5</v>
       </c>
-      <c r="AB80" s="21">
+      <c r="AB80" s="22">
         <f t="shared" si="44"/>
         <v>1</v>
       </c>
-      <c r="AC80" s="21">
+      <c r="AC80" s="22">
         <f>AB80*1000000+(AA80+100)*1000+Y80*10+1</f>
         <v>1095011</v>
       </c>
@@ -7519,16 +7531,16 @@
       <c r="C81" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="D81" s="16">
+      <c r="D81" s="17">
         <v>3.0</v>
       </c>
-      <c r="E81" s="16">
+      <c r="E81" s="17">
         <v>0.0</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="G81" s="18" t="s">
+      <c r="G81" s="19" t="s">
         <v>202</v>
       </c>
     </row>
@@ -7539,21 +7551,21 @@
       <c r="C82" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="17">
         <v>2.0</v>
       </c>
-      <c r="E82" s="16">
+      <c r="E82" s="17">
         <v>0.0</v>
       </c>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="G82" s="18" t="s">
+      <c r="G82" s="19" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="83" ht="18.0" customHeight="1">
-      <c r="B83" s="24" t="s">
+      <c r="B83" s="25" t="s">
         <v>204</v>
       </c>
       <c r="C83" s="4"/>
@@ -7599,94 +7611,94 @@
       <c r="C84" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="17">
         <v>2.0</v>
       </c>
-      <c r="E84" s="16">
+      <c r="E84" s="17">
         <v>0.0</v>
       </c>
-      <c r="F84" s="17" t="s">
+      <c r="F84" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="G84" s="18" t="s">
+      <c r="G84" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I84" s="19">
+      <c r="I84" s="20">
         <v>1.0</v>
       </c>
-      <c r="J84" s="20" t="str">
+      <c r="J84" s="21" t="str">
         <f t="array" ref="J84">INDEX(T84:T87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>Inglaterra 🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
       </c>
-      <c r="K84" s="19">
+      <c r="K84" s="20">
         <f t="array" ref="K84">INDEX(U84:U87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="L84" s="19">
+      <c r="L84" s="20">
         <f t="array" ref="L84">INDEX(V84:V87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="M84" s="19">
+      <c r="M84" s="20">
         <f t="array" ref="M84">INDEX(W84:W87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="N84" s="19">
+      <c r="N84" s="20">
         <f t="array" ref="N84">INDEX(X84:X87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="O84" s="19">
+      <c r="O84" s="20">
         <f t="array" ref="O84">INDEX(Y84:Y87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>9</v>
       </c>
-      <c r="P84" s="19">
+      <c r="P84" s="20">
         <f t="array" ref="P84">INDEX(Z84:Z87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="Q84" s="19">
+      <c r="Q84" s="20">
         <f t="array" ref="Q84">INDEX(AA84:AA87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>9</v>
       </c>
-      <c r="R84" s="19">
+      <c r="R84" s="20">
         <f t="array" ref="R84">INDEX(AB84:AB87,MATCH(LARGE(AC84:AC87,1),AC84:AC87,0))</f>
         <v>9</v>
       </c>
-      <c r="T84" s="21" t="str">
+      <c r="T84" s="22" t="str">
         <f>B84</f>
         <v>Inglaterra 🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
       </c>
-      <c r="U84" s="21">
+      <c r="U84" s="22">
         <f>IF(AND(ISNUMBER(D84),ISNUMBER(E84)),1,0)+IF(AND(ISNUMBER(D86),ISNUMBER(E86)),1,0)+IF(AND(ISNUMBER(D88),ISNUMBER(E88)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V84" s="21">
+      <c r="V84" s="22">
         <f>IF(AND(ISNUMBER(D84),ISNUMBER(E84),D84&gt;E84),1,0)+IF(AND(ISNUMBER(D86),ISNUMBER(E86),D86&gt;E86),1,0)+IF(AND(ISNUMBER(D88),ISNUMBER(E88),D88&gt;E88),1,0)</f>
         <v>3</v>
       </c>
-      <c r="W84" s="21">
+      <c r="W84" s="22">
         <f>IF(AND(ISNUMBER(D84),ISNUMBER(E84),D84=E84),1,0)+IF(AND(ISNUMBER(D86),ISNUMBER(E86),D86=E86),1,0)+IF(AND(ISNUMBER(D88),ISNUMBER(E88),D88=E88),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X84" s="21">
+      <c r="X84" s="22">
         <f t="shared" ref="X84:X87" si="46">U84-V84-W84</f>
         <v>0</v>
       </c>
-      <c r="Y84" s="21">
+      <c r="Y84" s="22">
         <f t="shared" ref="Y84:Z84" si="45">IF(ISNUMBER(D84),D84,0)+IF(ISNUMBER(D86),D86,0)+IF(ISNUMBER(D88),D88,0)</f>
         <v>9</v>
       </c>
-      <c r="Z84" s="21">
+      <c r="Z84" s="22">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="AA84" s="21">
+      <c r="AA84" s="22">
         <f t="shared" ref="AA84:AA87" si="47">Y84-Z84</f>
         <v>9</v>
       </c>
-      <c r="AB84" s="21">
+      <c r="AB84" s="22">
         <f t="shared" ref="AB84:AB87" si="48">V84*3+W84</f>
         <v>9</v>
       </c>
-      <c r="AC84" s="21">
+      <c r="AC84" s="22">
         <f>AB84*1000000+(AA84+100)*1000+Y84*10+4</f>
         <v>9109094</v>
       </c>
@@ -7698,94 +7710,94 @@
       <c r="C85" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="17">
         <v>2.0</v>
       </c>
-      <c r="E85" s="16">
+      <c r="E85" s="17">
         <v>1.0</v>
       </c>
-      <c r="F85" s="17" t="s">
+      <c r="F85" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="G85" s="18" t="s">
+      <c r="G85" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I85" s="19">
+      <c r="I85" s="20">
         <v>2.0</v>
       </c>
-      <c r="J85" s="20" t="str">
+      <c r="J85" s="21" t="str">
         <f t="array" ref="J85">INDEX(T84:T87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>🇭🇷 Croacia</v>
       </c>
-      <c r="K85" s="19">
+      <c r="K85" s="20">
         <f t="array" ref="K85">INDEX(U84:U87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="20">
         <f t="array" ref="L85">INDEX(V84:V87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>2</v>
       </c>
-      <c r="M85" s="19">
+      <c r="M85" s="20">
         <f t="array" ref="M85">INDEX(W84:W87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="N85" s="19">
+      <c r="N85" s="20">
         <f t="array" ref="N85">INDEX(X84:X87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>1</v>
       </c>
-      <c r="O85" s="19">
+      <c r="O85" s="20">
         <f t="array" ref="O85">INDEX(Y84:Y87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="P85" s="19">
+      <c r="P85" s="20">
         <f t="array" ref="P85">INDEX(Z84:Z87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>2</v>
       </c>
-      <c r="Q85" s="19">
+      <c r="Q85" s="20">
         <f t="array" ref="Q85">INDEX(AA84:AA87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>1</v>
       </c>
-      <c r="R85" s="19">
+      <c r="R85" s="20">
         <f t="array" ref="R85">INDEX(AB84:AB87,MATCH(LARGE(AC84:AC87,2),AC84:AC87,0))</f>
         <v>6</v>
       </c>
-      <c r="T85" s="21" t="str">
+      <c r="T85" s="22" t="str">
         <f>F84</f>
         <v>🇭🇷 Croacia</v>
       </c>
-      <c r="U85" s="21">
+      <c r="U85" s="22">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(E87)),1,0)+IF(AND(ISNUMBER(D89),ISNUMBER(E89)),1,0)+IF(AND(ISNUMBER(D84),ISNUMBER(E84)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V85" s="21">
+      <c r="V85" s="22">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(E87),D87&gt;E87),1,0)+IF(AND(ISNUMBER(D89),ISNUMBER(E89),D89&gt;E89),1,0)+IF(AND(ISNUMBER(D84),ISNUMBER(E84),E84&gt;D84),1,0)</f>
         <v>2</v>
       </c>
-      <c r="W85" s="21">
+      <c r="W85" s="22">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(E87),D87=E87),1,0)+IF(AND(ISNUMBER(D89),ISNUMBER(E89),D89=E89),1,0)+IF(AND(ISNUMBER(D84),ISNUMBER(E84),D84=E84),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X85" s="21">
+      <c r="X85" s="22">
         <f t="shared" si="46"/>
         <v>1</v>
       </c>
-      <c r="Y85" s="21">
+      <c r="Y85" s="22">
         <f>IF(ISNUMBER(D87),D87,0)+IF(ISNUMBER(D89),D89,0)+IF(ISNUMBER(E84),E84,0)</f>
         <v>3</v>
       </c>
-      <c r="Z85" s="21">
+      <c r="Z85" s="22">
         <f>IF(ISNUMBER(E87),E87,0)+IF(ISNUMBER(E89),E89,0)+IF(ISNUMBER(D84),D84,0)</f>
         <v>2</v>
       </c>
-      <c r="AA85" s="21">
+      <c r="AA85" s="22">
         <f t="shared" si="47"/>
         <v>1</v>
       </c>
-      <c r="AB85" s="21">
+      <c r="AB85" s="22">
         <f t="shared" si="48"/>
         <v>6</v>
       </c>
-      <c r="AC85" s="21">
+      <c r="AC85" s="22">
         <f>AB85*1000000+(AA85+100)*1000+Y85*10+3</f>
         <v>6101033</v>
       </c>
@@ -7797,94 +7809,94 @@
       <c r="C86" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="D86" s="16">
+      <c r="D86" s="17">
         <v>3.0</v>
       </c>
-      <c r="E86" s="16">
+      <c r="E86" s="17">
         <v>0.0</v>
       </c>
-      <c r="F86" s="17" t="s">
+      <c r="F86" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="G86" s="18" t="s">
+      <c r="G86" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="I86" s="22">
+      <c r="I86" s="23">
         <v>3.0</v>
       </c>
-      <c r="J86" s="23" t="str">
+      <c r="J86" s="24" t="str">
         <f t="array" ref="J86">INDEX(T84:T87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>Ghana 🇬🇭</v>
       </c>
-      <c r="K86" s="22">
+      <c r="K86" s="23">
         <f t="array" ref="K86">INDEX(U84:U87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="L86" s="22">
+      <c r="L86" s="23">
         <f t="array" ref="L86">INDEX(V84:V87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>1</v>
       </c>
-      <c r="M86" s="22">
+      <c r="M86" s="23">
         <f t="array" ref="M86">INDEX(W84:W87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="N86" s="22">
+      <c r="N86" s="23">
         <f t="array" ref="N86">INDEX(X84:X87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>2</v>
       </c>
-      <c r="O86" s="22">
+      <c r="O86" s="23">
         <f t="array" ref="O86">INDEX(Y84:Y87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>2</v>
       </c>
-      <c r="P86" s="22">
+      <c r="P86" s="23">
         <f t="array" ref="P86">INDEX(Z84:Z87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>5</v>
       </c>
-      <c r="Q86" s="22">
+      <c r="Q86" s="23">
         <f t="array" ref="Q86">INDEX(AA84:AA87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>-3</v>
       </c>
-      <c r="R86" s="22">
+      <c r="R86" s="23">
         <f t="array" ref="R86">INDEX(AB84:AB87,MATCH(LARGE(AC84:AC87,3),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="T86" s="21" t="str">
+      <c r="T86" s="22" t="str">
         <f>B85</f>
         <v>Ghana 🇬🇭</v>
       </c>
-      <c r="U86" s="21">
+      <c r="U86" s="22">
         <f>IF(AND(ISNUMBER(D85),ISNUMBER(E85)),1,0)+IF(AND(ISNUMBER(D86),ISNUMBER(E86)),1,0)+IF(AND(ISNUMBER(D89),ISNUMBER(E89)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V86" s="21">
+      <c r="V86" s="22">
         <f>IF(AND(ISNUMBER(D85),ISNUMBER(E85),D85&gt;E85),1,0)+IF(AND(ISNUMBER(D86),ISNUMBER(E86),E86&gt;D86),1,0)+IF(AND(ISNUMBER(D89),ISNUMBER(E89),E89&gt;D89),1,0)</f>
         <v>1</v>
       </c>
-      <c r="W86" s="21">
+      <c r="W86" s="22">
         <f>IF(AND(ISNUMBER(D85),ISNUMBER(E85),D85=E85),1,0)+IF(AND(ISNUMBER(D86),ISNUMBER(E86),D86=E86),1,0)+IF(AND(ISNUMBER(D89),ISNUMBER(E89),D89=E89),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X86" s="21">
+      <c r="X86" s="22">
         <f t="shared" si="46"/>
         <v>2</v>
       </c>
-      <c r="Y86" s="21">
+      <c r="Y86" s="22">
         <f>IF(ISNUMBER(D85),D85,0)+IF(ISNUMBER(E86),E86,0)+IF(ISNUMBER(E89),E89,0)</f>
         <v>2</v>
       </c>
-      <c r="Z86" s="21">
+      <c r="Z86" s="22">
         <f>IF(ISNUMBER(E85),E85,0)+IF(ISNUMBER(D86),D86,0)+IF(ISNUMBER(D89),D89,0)</f>
         <v>5</v>
       </c>
-      <c r="AA86" s="21">
+      <c r="AA86" s="22">
         <f t="shared" si="47"/>
         <v>-3</v>
       </c>
-      <c r="AB86" s="21">
+      <c r="AB86" s="22">
         <f t="shared" si="48"/>
         <v>3</v>
       </c>
-      <c r="AC86" s="21">
+      <c r="AC86" s="22">
         <f>AB86*1000000+(AA86+100)*1000+Y86*10+2</f>
         <v>3097022</v>
       </c>
@@ -7896,94 +7908,94 @@
       <c r="C87" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="D87" s="16">
+      <c r="D87" s="17">
         <v>2.0</v>
       </c>
-      <c r="E87" s="16">
+      <c r="E87" s="17">
         <v>0.0</v>
       </c>
-      <c r="F87" s="17" t="s">
+      <c r="F87" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="G87" s="18" t="s">
+      <c r="G87" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="I87" s="22">
+      <c r="I87" s="23">
         <v>4.0</v>
       </c>
-      <c r="J87" s="23" t="str">
+      <c r="J87" s="24" t="str">
         <f t="array" ref="J87">INDEX(T84:T87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>🇵🇦 Panamá</v>
       </c>
-      <c r="K87" s="22">
+      <c r="K87" s="23">
         <f t="array" ref="K87">INDEX(U84:U87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="L87" s="22">
+      <c r="L87" s="23">
         <f t="array" ref="L87">INDEX(V84:V87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="M87" s="22">
+      <c r="M87" s="23">
         <f t="array" ref="M87">INDEX(W84:W87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="N87" s="22">
+      <c r="N87" s="23">
         <f t="array" ref="N87">INDEX(X84:X87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>3</v>
       </c>
-      <c r="O87" s="22">
+      <c r="O87" s="23">
         <f t="array" ref="O87">INDEX(Y84:Y87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>1</v>
       </c>
-      <c r="P87" s="22">
+      <c r="P87" s="23">
         <f t="array" ref="P87">INDEX(Z84:Z87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>8</v>
       </c>
-      <c r="Q87" s="22">
+      <c r="Q87" s="23">
         <f t="array" ref="Q87">INDEX(AA84:AA87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>-7</v>
       </c>
-      <c r="R87" s="22">
+      <c r="R87" s="23">
         <f t="array" ref="R87">INDEX(AB84:AB87,MATCH(LARGE(AC84:AC87,4),AC84:AC87,0))</f>
         <v>0</v>
       </c>
-      <c r="T87" s="21" t="str">
+      <c r="T87" s="22" t="str">
         <f>F85</f>
         <v>🇵🇦 Panamá</v>
       </c>
-      <c r="U87" s="21">
+      <c r="U87" s="22">
         <f>IF(AND(ISNUMBER(D85),ISNUMBER(E85)),1,0)+IF(AND(ISNUMBER(D87),ISNUMBER(E87)),1,0)+IF(AND(ISNUMBER(D88),ISNUMBER(E88)),1,0)</f>
         <v>3</v>
       </c>
-      <c r="V87" s="21">
+      <c r="V87" s="22">
         <f>IF(AND(ISNUMBER(D85),ISNUMBER(E85),E85&gt;D85),1,0)+IF(AND(ISNUMBER(D87),ISNUMBER(E87),E87&gt;D87),1,0)+IF(AND(ISNUMBER(D88),ISNUMBER(E88),E88&gt;D88),1,0)</f>
         <v>0</v>
       </c>
-      <c r="W87" s="21">
+      <c r="W87" s="22">
         <f>IF(AND(ISNUMBER(D85),ISNUMBER(E85),D85=E85),1,0)+IF(AND(ISNUMBER(D87),ISNUMBER(E87),D87=E87),1,0)+IF(AND(ISNUMBER(D88),ISNUMBER(E88),D88=E88),1,0)</f>
         <v>0</v>
       </c>
-      <c r="X87" s="21">
+      <c r="X87" s="22">
         <f t="shared" si="46"/>
         <v>3</v>
       </c>
-      <c r="Y87" s="21">
+      <c r="Y87" s="22">
         <f>IF(ISNUMBER(E85),E85,0)+IF(ISNUMBER(E87),E87,0)+IF(ISNUMBER(E88),E88,0)</f>
         <v>1</v>
       </c>
-      <c r="Z87" s="21">
+      <c r="Z87" s="22">
         <f>IF(ISNUMBER(D85),D85,0)+IF(ISNUMBER(D87),D87,0)+IF(ISNUMBER(D88),D88,0)</f>
         <v>8</v>
       </c>
-      <c r="AA87" s="21">
+      <c r="AA87" s="22">
         <f t="shared" si="47"/>
         <v>-7</v>
       </c>
-      <c r="AB87" s="21">
+      <c r="AB87" s="22">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="AC87" s="21">
+      <c r="AC87" s="22">
         <f>AB87*1000000+(AA87+100)*1000+Y87*10+1</f>
         <v>93011</v>
       </c>
@@ -7995,16 +8007,16 @@
       <c r="C88" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="D88" s="16">
+      <c r="D88" s="17">
         <v>4.0</v>
       </c>
-      <c r="E88" s="16">
+      <c r="E88" s="17">
         <v>0.0</v>
       </c>
-      <c r="F88" s="17" t="s">
+      <c r="F88" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="G88" s="18" t="s">
+      <c r="G88" s="19" t="s">
         <v>218</v>
       </c>
     </row>
@@ -8015,16 +8027,16 @@
       <c r="C89" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="D89" s="16">
+      <c r="D89" s="17">
         <v>1.0</v>
       </c>
-      <c r="E89" s="16">
+      <c r="E89" s="17">
         <v>0.0</v>
       </c>
-      <c r="F89" s="17" t="s">
+      <c r="F89" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="G89" s="18" t="s">
+      <c r="G89" s="19" t="s">
         <v>218</v>
       </c>
     </row>
@@ -8992,37 +9004,43 @@
       <c r="D1" s="5"/>
     </row>
     <row r="2" ht="27.75" customHeight="1">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>221</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="9"/>
     </row>
     <row r="3" ht="25.5" customHeight="1">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28" t="s">
+      <c r="C3" s="28" t="s">
         <v>223</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="4" ht="25.5" customHeight="1">
-      <c r="B4" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>225</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1">
-      <c r="B5" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28" t="s">
-        <v>227</v>
+      <c r="B5" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/pronosticos/plantilla_Antonio.xlsx
+++ b/pronosticos/plantilla_Antonio.xlsx
@@ -689,7 +689,7 @@
     <t>MVP del Torneo</t>
   </si>
   <si>
-    <t>Vitinha</t>
+    <t>Pedri</t>
   </si>
   <si>
     <t>Mejor jugador del torneo (FIFA)</t>
